--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://shujitsuacjp-my.sharepoint.com/personal/s1624075mx_shujitsu_ac_jp/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{845C463B-F84E-3746-B36D-C1D5E6FB1318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3F1276E-B94A-4349-B1BD-C271E0CD03EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,10 @@
     <sheet name="能力データ(100打席以上)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'能力データ(100打席以上)'!$A$1:$F$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'能力データ(100打席以上)'!$B$1:$B$231</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="490">
   <si>
     <t>選手名</t>
   </si>
@@ -225,9 +226,6 @@
   </si>
   <si>
     <t>中川圭太</t>
-  </si>
-  <si>
-    <t>LF:30 / CF:33 / RF:57</t>
   </si>
   <si>
     <t>黒川史陽</t>
@@ -1904,6 +1902,92 @@
   </si>
   <si>
     <t>C:44 / 1B:44 / LF:51 / RF:58</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>村上宗隆</t>
+    <rPh sb="0" eb="2">
+      <t>ムラカミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ムネタカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MLB</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>岡本和真</t>
+    <rPh sb="0" eb="2">
+      <t>オカモト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カズマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大谷翔平</t>
+    <rPh sb="0" eb="2">
+      <t>オオタニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウヘイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吉田正尚</t>
+    <rPh sb="0" eb="2">
+      <t>ヨシダ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マサタカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鈴木誠也</t>
+    <rPh sb="0" eb="2">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイヤ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヌートバー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1B:51 /  3B:41</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1B:61 / 3B:66 / LF:42</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LF:42 / RF:42</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LF:38</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CF:48 / RF:75</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LF:68 / CF:78 / RF:78</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1B:30 / LF:30 / CF:33 / RF:57</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2002,6 +2086,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2289,19 +2377,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F225"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F231"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.99609375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="53.04296875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="15" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="53" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2338,10 +2427,10 @@
         <v>66</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -2358,10 +2447,10 @@
         <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.1">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2378,10 +2467,10 @@
         <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2398,10 +2487,10 @@
         <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2418,10 +2507,10 @@
         <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2438,10 +2527,10 @@
         <v>56</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2461,7 +2550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2478,10 +2567,10 @@
         <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.1">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -2498,10 +2587,10 @@
         <v>55</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -2518,10 +2607,10 @@
         <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2538,10 +2627,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -2558,10 +2647,10 @@
         <v>34</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2578,10 +2667,10 @@
         <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -2598,10 +2687,10 @@
         <v>78</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -2618,10 +2707,10 @@
         <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
@@ -2638,10 +2727,10 @@
         <v>61</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -2658,12 +2747,12 @@
         <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>39</v>
@@ -2678,10 +2767,10 @@
         <v>72</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.1">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2698,10 +2787,10 @@
         <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -2718,10 +2807,10 @@
         <v>32</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -2738,10 +2827,10 @@
         <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -2761,7 +2850,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -2778,10 +2867,10 @@
         <v>55</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -2798,10 +2887,10 @@
         <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -2818,10 +2907,10 @@
         <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -2838,10 +2927,10 @@
         <v>70</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -2858,10 +2947,10 @@
         <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -2878,12 +2967,12 @@
         <v>37</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>39</v>
@@ -2898,12 +2987,12 @@
         <v>28</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>7</v>
@@ -2918,10 +3007,10 @@
         <v>77</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -2941,7 +3030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -2958,10 +3047,10 @@
         <v>62</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -2978,10 +3067,10 @@
         <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -2998,10 +3087,10 @@
         <v>58</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
@@ -3018,12 +3107,12 @@
         <v>79</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3038,12 +3127,12 @@
         <v>39</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="2" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A38" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>49</v>
@@ -3058,10 +3147,10 @@
         <v>54</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
@@ -3078,12 +3167,12 @@
         <v>60</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>29</v>
@@ -3098,12 +3187,12 @@
         <v>61</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>41</v>
@@ -3118,12 +3207,12 @@
         <v>21</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>29</v>
@@ -3138,10 +3227,10 @@
         <v>32</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
@@ -3161,7 +3250,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -3178,10 +3267,10 @@
         <v>55</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>59</v>
       </c>
@@ -3198,10 +3287,10 @@
         <v>52</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -3218,10 +3307,10 @@
         <v>40</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -3241,7 +3330,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>60</v>
       </c>
@@ -3258,10 +3347,10 @@
         <v>42</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>62</v>
       </c>
@@ -3278,12 +3367,12 @@
         <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A50" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>27</v>
@@ -3298,12 +3387,12 @@
         <v>33</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>43</v>
@@ -3318,12 +3407,12 @@
         <v>60</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>33</v>
@@ -3338,12 +3427,12 @@
         <v>70</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>33</v>
@@ -3358,12 +3447,12 @@
         <v>24</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>41</v>
@@ -3378,12 +3467,12 @@
         <v>80</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>9</v>
@@ -3398,12 +3487,12 @@
         <v>48</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>43</v>
@@ -3418,12 +3507,12 @@
         <v>45</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3438,12 +3527,12 @@
         <v>51</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>39</v>
@@ -3458,12 +3547,12 @@
         <v>46</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>27</v>
@@ -3478,12 +3567,12 @@
         <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>11</v>
@@ -3498,12 +3587,12 @@
         <v>71</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
@@ -3518,12 +3607,12 @@
         <v>34</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.1">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>9</v>
@@ -3538,12 +3627,12 @@
         <v>47</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>27</v>
@@ -3558,12 +3647,12 @@
         <v>30</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>27</v>
@@ -3578,12 +3667,12 @@
         <v>66</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>39</v>
@@ -3598,12 +3687,12 @@
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>41</v>
@@ -3618,12 +3707,12 @@
         <v>90</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>49</v>
@@ -3638,12 +3727,12 @@
         <v>30</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>41</v>
@@ -3658,12 +3747,12 @@
         <v>34</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>29</v>
@@ -3678,12 +3767,12 @@
         <v>30</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>49</v>
@@ -3698,12 +3787,12 @@
         <v>30</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>29</v>
@@ -3718,12 +3807,12 @@
         <v>62</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>39</v>
@@ -3738,12 +3827,12 @@
         <v>66</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>29</v>
@@ -3758,12 +3847,12 @@
         <v>52</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>41</v>
@@ -3778,12 +3867,12 @@
         <v>53</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>39</v>
@@ -3798,12 +3887,12 @@
         <v>30</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>9</v>
@@ -3818,12 +3907,12 @@
         <v>55</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>14</v>
@@ -3838,12 +3927,12 @@
         <v>58</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -3858,12 +3947,12 @@
         <v>42</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>33</v>
@@ -3878,12 +3967,12 @@
         <v>41</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>41</v>
@@ -3898,12 +3987,12 @@
         <v>60</v>
       </c>
       <c r="F80" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="2" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A81" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>43</v>
@@ -3918,12 +4007,12 @@
         <v>26</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>29</v>
@@ -3938,12 +4027,12 @@
         <v>49</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>49</v>
@@ -3958,12 +4047,12 @@
         <v>40</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>11</v>
@@ -3978,12 +4067,12 @@
         <v>46</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>43</v>
@@ -3998,12 +4087,12 @@
         <v>52</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>49</v>
@@ -4018,12 +4107,12 @@
         <v>78</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>43</v>
@@ -4038,12 +4127,12 @@
         <v>71</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>7</v>
@@ -4058,12 +4147,12 @@
         <v>77</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.1">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>14</v>
@@ -4078,12 +4167,12 @@
         <v>85</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>9</v>
@@ -4098,12 +4187,12 @@
         <v>58</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>29</v>
@@ -4118,12 +4207,12 @@
         <v>54</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>14</v>
@@ -4138,12 +4227,12 @@
         <v>48</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
@@ -4158,12 +4247,12 @@
         <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>27</v>
@@ -4178,12 +4267,12 @@
         <v>30</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>27</v>
@@ -4198,12 +4287,12 @@
         <v>34</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>49</v>
@@ -4218,12 +4307,12 @@
         <v>71</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>9</v>
@@ -4238,12 +4327,12 @@
         <v>29</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>9</v>
@@ -4258,12 +4347,12 @@
         <v>41</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>43</v>
@@ -4278,12 +4367,12 @@
         <v>36</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>49</v>
@@ -4298,12 +4387,12 @@
         <v>27</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>11</v>
@@ -4318,12 +4407,12 @@
         <v>77</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>7</v>
@@ -4338,12 +4427,12 @@
         <v>53</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>41</v>
@@ -4358,12 +4447,12 @@
         <v>66</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>49</v>
@@ -4378,12 +4467,12 @@
         <v>41</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>43</v>
@@ -4398,12 +4487,12 @@
         <v>73</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>16</v>
@@ -4418,12 +4507,12 @@
         <v>77</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>41</v>
@@ -4438,12 +4527,12 @@
         <v>58</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>39</v>
@@ -4458,12 +4547,12 @@
         <v>71</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>39</v>
@@ -4478,12 +4567,12 @@
         <v>30</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>39</v>
@@ -4498,12 +4587,12 @@
         <v>71</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>7</v>
@@ -4518,12 +4607,12 @@
         <v>31</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -4538,12 +4627,12 @@
         <v>30</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>33</v>
@@ -4558,12 +4647,12 @@
         <v>30</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>39</v>
@@ -4578,12 +4667,12 @@
         <v>66</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>11</v>
@@ -4598,12 +4687,12 @@
         <v>25</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>41</v>
@@ -4618,12 +4707,12 @@
         <v>28</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
@@ -4638,12 +4727,12 @@
         <v>71</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>33</v>
@@ -4658,12 +4747,12 @@
         <v>30</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>49</v>
@@ -4678,12 +4767,12 @@
         <v>60</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>9</v>
@@ -4698,12 +4787,12 @@
         <v>33</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>39</v>
@@ -4718,12 +4807,12 @@
         <v>75</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
@@ -4738,12 +4827,12 @@
         <v>82</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>9</v>
@@ -4758,12 +4847,12 @@
         <v>78</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>33</v>
@@ -4778,12 +4867,12 @@
         <v>41</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>16</v>
@@ -4798,12 +4887,12 @@
         <v>58</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>39</v>
@@ -4818,12 +4907,12 @@
         <v>58</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>43</v>
@@ -4838,12 +4927,12 @@
         <v>30</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>49</v>
@@ -4858,12 +4947,12 @@
         <v>34</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>33</v>
@@ -4878,12 +4967,12 @@
         <v>66</v>
       </c>
       <c r="F129" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="2" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A130" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>16</v>
@@ -4898,12 +4987,12 @@
         <v>70</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>14</v>
@@ -4918,12 +5007,12 @@
         <v>67</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>33</v>
@@ -4938,12 +5027,12 @@
         <v>55</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>9</v>
@@ -4958,12 +5047,12 @@
         <v>70</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>33</v>
@@ -4978,12 +5067,12 @@
         <v>37</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>29</v>
@@ -4998,12 +5087,12 @@
         <v>72</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>29</v>
@@ -5018,12 +5107,12 @@
         <v>80</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>43</v>
@@ -5038,12 +5127,12 @@
         <v>72</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>7</v>
@@ -5058,12 +5147,12 @@
         <v>35</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>27</v>
@@ -5078,12 +5167,12 @@
         <v>30</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>16</v>
@@ -5098,12 +5187,12 @@
         <v>48</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>27</v>
@@ -5118,12 +5207,12 @@
         <v>72</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>29</v>
@@ -5138,12 +5227,12 @@
         <v>28</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>14</v>
@@ -5158,12 +5247,12 @@
         <v>69</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>7</v>
@@ -5178,12 +5267,12 @@
         <v>46</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>9</v>
@@ -5198,12 +5287,12 @@
         <v>30</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>49</v>
@@ -5218,12 +5307,12 @@
         <v>49</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>9</v>
@@ -5238,12 +5327,12 @@
         <v>94</v>
       </c>
       <c r="F147" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="2" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A148" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>43</v>
@@ -5258,12 +5347,12 @@
         <v>61</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>14</v>
@@ -5278,12 +5367,12 @@
         <v>30</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>7</v>
@@ -5298,12 +5387,12 @@
         <v>76</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.1">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>14</v>
@@ -5318,12 +5407,12 @@
         <v>21</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>11</v>
@@ -5338,12 +5427,12 @@
         <v>69</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>29</v>
@@ -5358,12 +5447,12 @@
         <v>71</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>7</v>
@@ -5378,12 +5467,12 @@
         <v>26</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>27</v>
@@ -5398,12 +5487,12 @@
         <v>44</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>49</v>
@@ -5418,12 +5507,12 @@
         <v>30</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>43</v>
@@ -5438,12 +5527,12 @@
         <v>61</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>14</v>
@@ -5458,12 +5547,12 @@
         <v>56</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>16</v>
@@ -5478,12 +5567,12 @@
         <v>80</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>7</v>
@@ -5498,12 +5587,12 @@
         <v>70</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>27</v>
@@ -5518,12 +5607,12 @@
         <v>74</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>9</v>
@@ -5538,12 +5627,12 @@
         <v>78</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>11</v>
@@ -5558,12 +5647,12 @@
         <v>59</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>33</v>
@@ -5578,12 +5667,12 @@
         <v>71</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>16</v>
@@ -5598,12 +5687,12 @@
         <v>30</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>33</v>
@@ -5618,12 +5707,12 @@
         <v>52</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>43</v>
@@ -5638,12 +5727,12 @@
         <v>61</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>43</v>
@@ -5658,12 +5747,12 @@
         <v>32</v>
       </c>
       <c r="F168" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="2" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A169" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>16</v>
@@ -5678,12 +5767,12 @@
         <v>30</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>9</v>
@@ -5698,12 +5787,12 @@
         <v>71</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>7</v>
@@ -5718,12 +5807,12 @@
         <v>52</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>41</v>
@@ -5738,12 +5827,12 @@
         <v>40</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>41</v>
@@ -5758,12 +5847,12 @@
         <v>55</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>43</v>
@@ -5778,12 +5867,12 @@
         <v>66</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>16</v>
@@ -5798,12 +5887,12 @@
         <v>30</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>16</v>
@@ -5818,12 +5907,12 @@
         <v>45</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>11</v>
@@ -5838,12 +5927,12 @@
         <v>30</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>43</v>
@@ -5858,15 +5947,15 @@
         <v>95</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A179" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B179" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="C179" s="3">
         <v>42</v>
@@ -5878,15 +5967,15 @@
         <v>69</v>
       </c>
       <c r="F179" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A180" s="3" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A180" s="3" t="s">
+      <c r="B180" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="C180" s="3">
         <v>39</v>
@@ -5898,15 +5987,15 @@
         <v>82</v>
       </c>
       <c r="F180" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A181" s="3" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A181" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="B181" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C181" s="3">
         <v>18</v>
@@ -5918,15 +6007,15 @@
         <v>28</v>
       </c>
       <c r="F181" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A182" s="3" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A182" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="B182" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C182" s="3">
         <v>33</v>
@@ -5938,15 +6027,15 @@
         <v>37</v>
       </c>
       <c r="F182" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="3" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A183" s="3" t="s">
-        <v>377</v>
-      </c>
       <c r="B183" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C183" s="3">
         <v>31</v>
@@ -5958,15 +6047,15 @@
         <v>51</v>
       </c>
       <c r="F183" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A184" s="3" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A184" s="3" t="s">
-        <v>379</v>
-      </c>
       <c r="B184" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C184" s="3">
         <v>38</v>
@@ -5978,15 +6067,15 @@
         <v>69</v>
       </c>
       <c r="F184" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A185" s="3" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A185" s="3" t="s">
-        <v>381</v>
-      </c>
       <c r="B185" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C185" s="3">
         <v>31</v>
@@ -5998,15 +6087,15 @@
         <v>46</v>
       </c>
       <c r="F185" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A186" s="3" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A186" s="3" t="s">
+      <c r="B186" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="C186" s="3">
         <v>44</v>
@@ -6018,15 +6107,15 @@
         <v>25</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.1">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C187" s="3">
         <v>39</v>
@@ -6038,15 +6127,15 @@
         <v>68</v>
       </c>
       <c r="F187" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A188" s="3" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A188" s="3" t="s">
-        <v>387</v>
-      </c>
       <c r="B188" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C188" s="3">
         <v>57</v>
@@ -6058,15 +6147,15 @@
         <v>58</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A189" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C189" s="3">
         <v>42</v>
@@ -6078,15 +6167,15 @@
         <v>70</v>
       </c>
       <c r="F189" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A190" s="3" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A190" s="3" t="s">
+      <c r="B190" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="C190" s="3">
         <v>16</v>
@@ -6098,15 +6187,15 @@
         <v>54</v>
       </c>
       <c r="F190" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A191" s="3" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A191" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="B191" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C191" s="3">
         <v>28</v>
@@ -6118,15 +6207,15 @@
         <v>66</v>
       </c>
       <c r="F191" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A192" s="3" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A192" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="B192" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C192" s="3">
         <v>52</v>
@@ -6138,15 +6227,15 @@
         <v>38</v>
       </c>
       <c r="F192" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A193" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A193" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="B193" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C193" s="3">
         <v>44</v>
@@ -6158,15 +6247,15 @@
         <v>61</v>
       </c>
       <c r="F193" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A194" s="3" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A194" s="3" t="s">
+      <c r="B194" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="C194" s="3">
         <v>39</v>
@@ -6178,15 +6267,15 @@
         <v>68</v>
       </c>
       <c r="F194" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A195" s="3" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A195" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="B195" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C195" s="3">
         <v>42</v>
@@ -6198,15 +6287,15 @@
         <v>64</v>
       </c>
       <c r="F195" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A196" s="3" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A196" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="B196" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C196" s="3">
         <v>50</v>
@@ -6218,15 +6307,15 @@
         <v>41</v>
       </c>
       <c r="F196" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A197" s="3" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A197" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="B197" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C197" s="3">
         <v>15</v>
@@ -6238,15 +6327,15 @@
         <v>28</v>
       </c>
       <c r="F197" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A198" s="3" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A198" s="3" t="s">
+      <c r="B198" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="C198" s="3">
         <v>41</v>
@@ -6258,15 +6347,15 @@
         <v>80</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.1">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A199" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C199" s="3">
         <v>54</v>
@@ -6278,15 +6367,15 @@
         <v>43</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A200" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C200" s="3">
         <v>57</v>
@@ -6298,15 +6387,15 @@
         <v>60</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A201" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C201" s="3">
         <v>49</v>
@@ -6318,15 +6407,15 @@
         <v>51</v>
       </c>
       <c r="F201" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A202" s="3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A202" s="3" t="s">
+      <c r="B202" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="C202" s="3">
         <v>43</v>
@@ -6338,15 +6427,15 @@
         <v>59</v>
       </c>
       <c r="F202" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A203" s="3" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A203" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="B203" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C203" s="3">
         <v>42</v>
@@ -6358,15 +6447,15 @@
         <v>63</v>
       </c>
       <c r="F203" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A204" s="3" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A204" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="B204" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C204" s="3">
         <v>46</v>
@@ -6378,15 +6467,15 @@
         <v>55</v>
       </c>
       <c r="F204" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A205" s="3" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A205" s="3" t="s">
-        <v>427</v>
-      </c>
       <c r="B205" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C205" s="3">
         <v>36</v>
@@ -6398,15 +6487,15 @@
         <v>41</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A206" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B206" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="C206" s="3">
         <v>37</v>
@@ -6418,15 +6507,15 @@
         <v>66</v>
       </c>
       <c r="F206" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A207" s="3" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A207" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="B207" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C207" s="3">
         <v>35</v>
@@ -6438,15 +6527,15 @@
         <v>51</v>
       </c>
       <c r="F207" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A208" s="3" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A208" s="3" t="s">
-        <v>437</v>
-      </c>
       <c r="B208" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C208" s="3">
         <v>41</v>
@@ -6458,15 +6547,15 @@
         <v>48</v>
       </c>
       <c r="F208" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A209" s="3" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A209" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="B209" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C209" s="3">
         <v>45</v>
@@ -6478,15 +6567,15 @@
         <v>79</v>
       </c>
       <c r="F209" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A210" s="3" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A210" s="3" t="s">
+      <c r="B210" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="C210" s="3">
         <v>59</v>
@@ -6498,15 +6587,15 @@
         <v>44</v>
       </c>
       <c r="F210" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A211" s="3" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A211" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="B211" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C211" s="3">
         <v>46</v>
@@ -6518,15 +6607,15 @@
         <v>22</v>
       </c>
       <c r="F211" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A212" s="3" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A212" s="3" t="s">
-        <v>446</v>
-      </c>
       <c r="B212" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C212" s="3">
         <v>57</v>
@@ -6538,15 +6627,15 @@
         <v>41</v>
       </c>
       <c r="F212" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A213" s="3" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A213" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="B213" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C213" s="3">
         <v>36</v>
@@ -6558,15 +6647,15 @@
         <v>55</v>
       </c>
       <c r="F213" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A214" s="3" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A214" s="3" t="s">
+      <c r="B214" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="C214" s="3">
         <v>38</v>
@@ -6578,15 +6667,15 @@
         <v>57</v>
       </c>
       <c r="F214" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A215" s="3" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A215" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="B215" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C215" s="3">
         <v>42</v>
@@ -6598,15 +6687,15 @@
         <v>66</v>
       </c>
       <c r="F215" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A216" s="3" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A216" s="3" t="s">
-        <v>455</v>
-      </c>
       <c r="B216" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C216" s="3">
         <v>41</v>
@@ -6618,15 +6707,15 @@
         <v>91</v>
       </c>
       <c r="F216" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A217" s="3" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A217" s="3" t="s">
-        <v>457</v>
-      </c>
       <c r="B217" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C217" s="3">
         <v>28</v>
@@ -6638,15 +6727,15 @@
         <v>80</v>
       </c>
       <c r="F217" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A218" s="3" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A218" s="3" t="s">
+      <c r="B218" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="C218" s="3">
         <v>51</v>
@@ -6658,15 +6747,15 @@
         <v>48</v>
       </c>
       <c r="F218" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A219" s="3" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A219" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="B219" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C219" s="3">
         <v>29</v>
@@ -6678,15 +6767,15 @@
         <v>84</v>
       </c>
       <c r="F219" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A220" s="3" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A220" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="B220" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C220" s="3">
         <v>22</v>
@@ -6698,15 +6787,15 @@
         <v>43</v>
       </c>
       <c r="F220" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A221" s="3" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A221" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="B221" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C221" s="3">
         <v>41</v>
@@ -6718,15 +6807,15 @@
         <v>60</v>
       </c>
       <c r="F221" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A222" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A222" s="3" t="s">
+      <c r="B222" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="C222" s="3">
         <v>47</v>
@@ -6738,15 +6827,15 @@
         <v>51</v>
       </c>
       <c r="F222" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A223" s="3" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A223" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="B223" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C223" s="3">
         <v>52</v>
@@ -6758,15 +6847,15 @@
         <v>41</v>
       </c>
       <c r="F223" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A224" s="3" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A224" s="3" t="s">
-        <v>473</v>
-      </c>
       <c r="B224" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C224" s="3">
         <v>44</v>
@@ -6778,15 +6867,15 @@
         <v>40</v>
       </c>
       <c r="F224" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A225" s="3" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A225" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="B225" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C225" s="3">
         <v>36</v>
@@ -6798,10 +6887,137 @@
         <v>57</v>
       </c>
       <c r="F225" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A226" s="3" t="s">
         <v>476</v>
       </c>
+      <c r="B226" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C226" s="3">
+        <v>77</v>
+      </c>
+      <c r="D226" s="3">
+        <v>92</v>
+      </c>
+      <c r="E226" s="3">
+        <v>63</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A227" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C227" s="3">
+        <v>79</v>
+      </c>
+      <c r="D227" s="3">
+        <v>86</v>
+      </c>
+      <c r="E227" s="3">
+        <v>43</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A228" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C228" s="3">
+        <v>89</v>
+      </c>
+      <c r="D228" s="3">
+        <v>98</v>
+      </c>
+      <c r="E228" s="3">
+        <v>77</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A229" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C229" s="3">
+        <v>85</v>
+      </c>
+      <c r="D229" s="3">
+        <v>79</v>
+      </c>
+      <c r="E229" s="3">
+        <v>41</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A230" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C230" s="3">
+        <v>84</v>
+      </c>
+      <c r="D230" s="3">
+        <v>84</v>
+      </c>
+      <c r="E230" s="3">
+        <v>72</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A231" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C231" s="3">
+        <v>73</v>
+      </c>
+      <c r="D231" s="3">
+        <v>75</v>
+      </c>
+      <c r="E231" s="3">
+        <v>81</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>488</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="オリックス"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7028,6 +7244,13 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
     <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7035,10 +7258,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3F1276E-B94A-4349-B1BD-C271E0CD03EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B677840-9CE5-4EA1-B1A0-5D73B51037B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'能力データ(100打席以上)'!$B$1:$B$231</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2430,7 +2429,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -2438,10 +2437,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2">
         <v>48</v>
@@ -2510,7 +2509,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2550,7 +2549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="2">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2">
         <v>87</v>
@@ -2570,7 +2569,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>72</v>
       </c>
       <c r="E10" s="2">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>330</v>
@@ -2610,7 +2609,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2630,7 +2629,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -2650,7 +2649,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2661,7 +2660,7 @@
         <v>72</v>
       </c>
       <c r="D14" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -2670,7 +2669,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -2681,7 +2680,7 @@
         <v>74</v>
       </c>
       <c r="D15" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2">
         <v>78</v>
@@ -2850,7 +2849,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -3350,7 +3349,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>62</v>
       </c>
@@ -3570,7 +3569,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
         <v>89</v>
       </c>
@@ -3590,7 +3589,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
         <v>97</v>
       </c>
@@ -3910,7 +3909,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
         <v>122</v>
       </c>
@@ -3921,7 +3920,7 @@
         <v>52</v>
       </c>
       <c r="D77" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E77" s="2">
         <v>58</v>
@@ -4050,7 +4049,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
         <v>131</v>
       </c>
@@ -4150,7 +4149,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
         <v>129</v>
       </c>
@@ -4210,7 +4209,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
         <v>160</v>
       </c>
@@ -4390,7 +4389,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
         <v>150</v>
       </c>
@@ -4670,7 +4669,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
         <v>119</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>188</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
         <v>184</v>
       </c>
@@ -5350,7 +5349,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
         <v>162</v>
       </c>
@@ -5390,7 +5389,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
         <v>195</v>
       </c>
@@ -5410,7 +5409,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
         <v>197</v>
       </c>
@@ -5530,7 +5529,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
         <v>193</v>
       </c>
@@ -5538,7 +5537,7 @@
         <v>14</v>
       </c>
       <c r="C158" s="2">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D158" s="2">
         <v>46</v>
@@ -5630,7 +5629,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
         <v>231</v>
       </c>
@@ -5910,7 +5909,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
         <v>229</v>
       </c>
@@ -6730,7 +6729,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A218" s="3" t="s">
         <v>458</v>
       </c>
@@ -6750,7 +6749,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A219" s="3" t="s">
         <v>461</v>
       </c>
@@ -6770,7 +6769,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A220" s="3" t="s">
         <v>463</v>
       </c>
@@ -6790,7 +6789,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A221" s="3" t="s">
         <v>465</v>
       </c>
@@ -6810,7 +6809,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A222" s="3" t="s">
         <v>467</v>
       </c>
@@ -6830,7 +6829,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A223" s="3" t="s">
         <v>470</v>
       </c>
@@ -6850,7 +6849,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A224" s="3" t="s">
         <v>472</v>
       </c>
@@ -6870,7 +6869,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A225" s="3" t="s">
         <v>474</v>
       </c>
@@ -7014,7 +7013,7 @@
   <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="オリックス"/>
+        <filter val="ソフトバンク"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7024,6 +7023,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B56F6E2A19A2F74190C4E1D46B40D305" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="41a44f59d3b68d1f18012b98926b6f28">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xmlns:ns4="1212b74f-52fc-4973-8f22-7750ea9e0eb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e80f7c3813526ed05737851d7f7b407" ns3:_="" ns4:_="">
     <xsd:import namespace="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
@@ -7218,24 +7234,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6C3AB4F-6546-4A10-9B21-424D4E5F957B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7253,29 +7277,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B677840-9CE5-4EA1-B1A0-5D73B51037B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8448916F-5192-4A75-873A-C1BA6A30E979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -947,9 +947,6 @@
     <t>C:71 / 1B:35</t>
   </si>
   <si>
-    <t>2B:48 / 3B:53 / SS:55 / CF:38 / RF:44</t>
-  </si>
-  <si>
     <t>1B:52 / LF:45 / CF:60 / RF:61</t>
   </si>
   <si>
@@ -1341,10 +1338,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>C61 / 1B:23</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>山本泰寛</t>
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
@@ -1987,6 +1980,14 @@
   </si>
   <si>
     <t>1B:30 / LF:30 / CF:33 / RF:57</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:61 / 1B:23</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2B:48 / 3B:53 / SS:38 / CF:55 / RF:44</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2376,7 +2377,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F231"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2446,10 +2446,10 @@
         <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2457,10 +2457,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2">
         <v>32</v>
@@ -2469,7 +2469,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2526,10 +2526,10 @@
         <v>56</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -2586,10 +2586,10 @@
         <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -2606,10 +2606,10 @@
         <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -2689,7 +2689,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2">
         <v>31</v>
@@ -2706,10 +2706,10 @@
         <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
@@ -2726,10 +2726,10 @@
         <v>61</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -2749,9 +2749,9 @@
         <v>257</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>39</v>
@@ -2769,7 +2769,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2786,10 +2786,10 @@
         <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -2866,10 +2866,10 @@
         <v>55</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -2886,10 +2886,10 @@
         <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -2946,10 +2946,10 @@
         <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -2966,10 +2966,10 @@
         <v>37</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>75</v>
       </c>
@@ -2997,19 +2997,19 @@
         <v>7</v>
       </c>
       <c r="C31" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2">
         <v>77</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -3046,10 +3046,10 @@
         <v>62</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -3066,10 +3066,10 @@
         <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -3086,10 +3086,10 @@
         <v>58</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
         <v>66</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
         <v>73</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
         <v>74</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
         <v>91</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -3266,10 +3266,10 @@
         <v>55</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>59</v>
       </c>
@@ -3286,10 +3286,10 @@
         <v>52</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>60</v>
       </c>
@@ -3346,10 +3346,10 @@
         <v>42</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>62</v>
       </c>
@@ -3366,10 +3366,10 @@
         <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
         <v>63</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
         <v>72</v>
       </c>
@@ -3406,10 +3406,10 @@
         <v>60</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
         <v>81</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
         <v>96</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -3466,10 +3466,10 @@
         <v>80</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
         <v>71</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
         <v>76</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
         <v>77</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
         <v>83</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
         <v>84</v>
       </c>
@@ -3566,10 +3566,10 @@
         <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
         <v>89</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
         <v>97</v>
       </c>
@@ -3606,10 +3606,10 @@
         <v>34</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
         <v>98</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
         <v>127</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
         <v>140</v>
       </c>
@@ -3666,10 +3666,10 @@
         <v>66</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
         <v>142</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
         <v>87</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
         <v>92</v>
       </c>
@@ -3746,10 +3746,10 @@
         <v>34</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
         <v>94</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
         <v>79</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
         <v>99</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
         <v>114</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
         <v>126</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
         <v>103</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
         <v>108</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
         <v>106</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
         <v>136</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
         <v>86</v>
       </c>
@@ -3966,10 +3966,10 @@
         <v>41</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
         <v>109</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
         <v>111</v>
       </c>
@@ -4006,10 +4006,10 @@
         <v>26</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
         <v>113</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
         <v>196</v>
       </c>
@@ -4046,10 +4046,10 @@
         <v>40</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
         <v>131</v>
       </c>
@@ -4066,10 +4066,10 @@
         <v>46</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
         <v>149</v>
       </c>
@@ -4086,10 +4086,10 @@
         <v>52</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
         <v>105</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
         <v>115</v>
       </c>
@@ -4126,10 +4126,10 @@
         <v>71</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
         <v>116</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>77</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -4169,7 +4169,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
         <v>133</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
         <v>138</v>
       </c>
@@ -4226,10 +4226,10 @@
         <v>48</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
         <v>102</v>
       </c>
@@ -4246,10 +4246,10 @@
         <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
         <v>118</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
         <v>123</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
         <v>141</v>
       </c>
@@ -4306,10 +4306,10 @@
         <v>71</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
         <v>168</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
         <v>218</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
         <v>104</v>
       </c>
@@ -4366,10 +4366,10 @@
         <v>36</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
         <v>117</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
         <v>150</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
         <v>192</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
         <v>199</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
         <v>205</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
         <v>101</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
         <v>121</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
         <v>125</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
         <v>128</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
         <v>144</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
         <v>147</v>
       </c>
@@ -4589,7 +4589,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
         <v>164</v>
       </c>
@@ -4606,10 +4606,10 @@
         <v>31</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
         <v>171</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
         <v>112</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
         <v>119</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
         <v>130</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
         <v>135</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
         <v>157</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
         <v>163</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
         <v>159</v>
       </c>
@@ -4783,13 +4783,13 @@
         <v>58</v>
       </c>
       <c r="E120" s="2">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
         <v>167</v>
       </c>
@@ -4806,10 +4806,10 @@
         <v>75</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
         <v>185</v>
       </c>
@@ -4826,10 +4826,10 @@
         <v>82</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
         <v>224</v>
       </c>
@@ -4846,10 +4846,10 @@
         <v>78</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
         <v>227</v>
       </c>
@@ -4866,10 +4866,10 @@
         <v>41</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
         <v>124</v>
       </c>
@@ -4886,10 +4886,10 @@
         <v>58</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
         <v>151</v>
       </c>
@@ -4906,10 +4906,10 @@
         <v>58</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
         <v>156</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
         <v>165</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
         <v>181</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>70</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -5009,7 +5009,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>216</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -5046,10 +5046,10 @@
         <v>70</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
         <v>172</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
         <v>175</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
         <v>182</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
         <v>241</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
         <v>146</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
         <v>152</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
         <v>177</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
         <v>186</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
         <v>203</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
         <v>190</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
         <v>198</v>
       </c>
@@ -5286,10 +5286,10 @@
         <v>30</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
         <v>206</v>
       </c>
@@ -5306,10 +5306,10 @@
         <v>49</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
         <v>213</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
         <v>215</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>61</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
@@ -5369,7 +5369,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
         <v>174</v>
       </c>
@@ -5406,10 +5406,10 @@
         <v>21</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
         <v>197</v>
       </c>
@@ -5426,10 +5426,10 @@
         <v>69</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
         <v>208</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
         <v>225</v>
       </c>
@@ -5466,10 +5466,10 @@
         <v>26</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
         <v>243</v>
       </c>
@@ -5486,10 +5486,10 @@
         <v>44</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
         <v>154</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
         <v>169</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>61</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
@@ -5549,7 +5549,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
         <v>207</v>
       </c>
@@ -5566,10 +5566,10 @@
         <v>80</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
         <v>239</v>
       </c>
@@ -5586,10 +5586,10 @@
         <v>70</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
         <v>212</v>
       </c>
@@ -5606,10 +5606,10 @@
         <v>74</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
         <v>228</v>
       </c>
@@ -5626,10 +5626,10 @@
         <v>78</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
         <v>231</v>
       </c>
@@ -5646,10 +5646,10 @@
         <v>59</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
         <v>201</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
         <v>220</v>
       </c>
@@ -5686,10 +5686,10 @@
         <v>30</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
         <v>223</v>
       </c>
@@ -5706,10 +5706,10 @@
         <v>52</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
         <v>236</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
         <v>232</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
         <v>234</v>
       </c>
@@ -5769,9 +5769,9 @@
         <v>235</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>9</v>
@@ -5786,10 +5786,10 @@
         <v>71</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
         <v>226</v>
       </c>
@@ -5806,10 +5806,10 @@
         <v>52</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
         <v>221</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
         <v>238</v>
       </c>
@@ -5846,10 +5846,10 @@
         <v>55</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
         <v>240</v>
       </c>
@@ -5866,10 +5866,10 @@
         <v>66</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
         <v>244</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
         <v>245</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
         <v>229</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A178" s="3" t="s">
         <v>268</v>
       </c>
@@ -5949,12 +5949,12 @@
         <v>269</v>
       </c>
     </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A179" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B179" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="C179" s="3">
         <v>42</v>
@@ -5966,15 +5966,15 @@
         <v>69</v>
       </c>
       <c r="F179" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A180" s="3" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A180" s="3" t="s">
+      <c r="B180" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="C180" s="3">
         <v>39</v>
@@ -5986,15 +5986,15 @@
         <v>82</v>
       </c>
       <c r="F180" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A181" s="3" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A181" s="3" t="s">
-        <v>372</v>
-      </c>
       <c r="B181" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C181" s="3">
         <v>18</v>
@@ -6006,15 +6006,15 @@
         <v>28</v>
       </c>
       <c r="F181" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A182" s="3" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="3" t="s">
-        <v>374</v>
-      </c>
       <c r="B182" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C182" s="3">
         <v>33</v>
@@ -6026,15 +6026,15 @@
         <v>37</v>
       </c>
       <c r="F182" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A183" s="3" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="B183" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C183" s="3">
         <v>31</v>
@@ -6046,15 +6046,15 @@
         <v>51</v>
       </c>
       <c r="F183" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A184" s="3" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A184" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="B184" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C184" s="3">
         <v>38</v>
@@ -6066,15 +6066,15 @@
         <v>69</v>
       </c>
       <c r="F184" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A185" s="3" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A185" s="3" t="s">
-        <v>380</v>
-      </c>
       <c r="B185" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C185" s="3">
         <v>31</v>
@@ -6086,15 +6086,15 @@
         <v>46</v>
       </c>
       <c r="F185" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A186" s="3" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A186" s="3" t="s">
+      <c r="B186" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>383</v>
       </c>
       <c r="C186" s="3">
         <v>44</v>
@@ -6106,15 +6106,15 @@
         <v>25</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A187" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C187" s="3">
         <v>39</v>
@@ -6126,15 +6126,15 @@
         <v>68</v>
       </c>
       <c r="F187" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A188" s="3" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A188" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="B188" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C188" s="3">
         <v>57</v>
@@ -6146,15 +6146,15 @@
         <v>58</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A189" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C189" s="3">
         <v>42</v>
@@ -6166,15 +6166,15 @@
         <v>70</v>
       </c>
       <c r="F189" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A190" s="3" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A190" s="3" t="s">
+      <c r="B190" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="C190" s="3">
         <v>16</v>
@@ -6186,15 +6186,15 @@
         <v>54</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A191" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C191" s="3">
         <v>28</v>
@@ -6206,15 +6206,15 @@
         <v>66</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C192" s="3">
         <v>52</v>
@@ -6226,15 +6226,15 @@
         <v>38</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A193" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C193" s="3">
         <v>44</v>
@@ -6246,15 +6246,15 @@
         <v>61</v>
       </c>
       <c r="F193" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A194" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B194" s="3" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A194" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="C194" s="3">
         <v>39</v>
@@ -6266,15 +6266,15 @@
         <v>68</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A195" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C195" s="3">
         <v>42</v>
@@ -6286,15 +6286,15 @@
         <v>64</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A196" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C196" s="3">
         <v>50</v>
@@ -6306,15 +6306,15 @@
         <v>41</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A197" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C197" s="3">
         <v>15</v>
@@ -6326,15 +6326,15 @@
         <v>28</v>
       </c>
       <c r="F197" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A198" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B198" s="3" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A198" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="C198" s="3">
         <v>41</v>
@@ -6346,15 +6346,15 @@
         <v>80</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A199" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C199" s="3">
         <v>54</v>
@@ -6366,15 +6366,15 @@
         <v>43</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A200" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C200" s="3">
         <v>57</v>
@@ -6386,15 +6386,15 @@
         <v>60</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A201" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C201" s="3">
         <v>49</v>
@@ -6406,15 +6406,15 @@
         <v>51</v>
       </c>
       <c r="F201" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A202" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B202" s="3" t="s">
         <v>418</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A202" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="C202" s="3">
         <v>43</v>
@@ -6426,15 +6426,15 @@
         <v>59</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A203" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C203" s="3">
         <v>42</v>
@@ -6446,15 +6446,15 @@
         <v>63</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A204" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C204" s="3">
         <v>46</v>
@@ -6466,15 +6466,15 @@
         <v>55</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A205" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C205" s="3">
         <v>36</v>
@@ -6486,15 +6486,15 @@
         <v>41</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A206" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C206" s="3">
         <v>37</v>
@@ -6506,15 +6506,15 @@
         <v>66</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A207" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C207" s="3">
         <v>35</v>
@@ -6526,15 +6526,15 @@
         <v>51</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A208" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C208" s="3">
         <v>41</v>
@@ -6546,15 +6546,15 @@
         <v>48</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A209" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C209" s="3">
         <v>45</v>
@@ -6566,15 +6566,15 @@
         <v>79</v>
       </c>
       <c r="F209" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A210" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B210" s="3" t="s">
         <v>439</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A210" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="C210" s="3">
         <v>59</v>
@@ -6586,15 +6586,15 @@
         <v>44</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A211" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C211" s="3">
         <v>46</v>
@@ -6606,15 +6606,15 @@
         <v>22</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A212" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C212" s="3">
         <v>57</v>
@@ -6626,15 +6626,15 @@
         <v>41</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A213" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C213" s="3">
         <v>36</v>
@@ -6646,15 +6646,15 @@
         <v>55</v>
       </c>
       <c r="F213" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A214" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B214" s="3" t="s">
         <v>448</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A214" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="C214" s="3">
         <v>38</v>
@@ -6666,15 +6666,15 @@
         <v>57</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A215" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C215" s="3">
         <v>42</v>
@@ -6686,15 +6686,15 @@
         <v>66</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A216" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C216" s="3">
         <v>41</v>
@@ -6706,15 +6706,15 @@
         <v>91</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A217" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C217" s="3">
         <v>28</v>
@@ -6726,15 +6726,15 @@
         <v>80</v>
       </c>
       <c r="F217" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A218" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B218" s="3" t="s">
         <v>457</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A218" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="C218" s="3">
         <v>51</v>
@@ -6746,15 +6746,15 @@
         <v>48</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A219" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C219" s="3">
         <v>29</v>
@@ -6766,15 +6766,15 @@
         <v>84</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A220" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C220" s="3">
         <v>22</v>
@@ -6786,15 +6786,15 @@
         <v>43</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A221" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C221" s="3">
         <v>41</v>
@@ -6806,15 +6806,15 @@
         <v>60</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A222" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C222" s="3">
         <v>47</v>
@@ -6826,15 +6826,15 @@
         <v>51</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A223" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C223" s="3">
         <v>52</v>
@@ -6846,15 +6846,15 @@
         <v>41</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A224" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C224" s="3">
         <v>44</v>
@@ -6866,15 +6866,15 @@
         <v>40</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A225" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C225" s="3">
         <v>36</v>
@@ -6886,15 +6886,15 @@
         <v>57</v>
       </c>
       <c r="F225" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A226" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B226" s="3" t="s">
         <v>475</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A226" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>477</v>
       </c>
       <c r="C226" s="3">
         <v>77</v>
@@ -6906,15 +6906,15 @@
         <v>63</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A227" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C227" s="3">
         <v>79</v>
@@ -6926,15 +6926,15 @@
         <v>43</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A228" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C228" s="3">
         <v>89</v>
@@ -6946,15 +6946,15 @@
         <v>77</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A229" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C229" s="3">
         <v>85</v>
@@ -6966,15 +6966,15 @@
         <v>41</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A230" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C230" s="3">
         <v>84</v>
@@ -6986,15 +6986,15 @@
         <v>72</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A231" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C231" s="3">
         <v>73</v>
@@ -7006,17 +7006,11 @@
         <v>81</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="ソフトバンク"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8448916F-5192-4A75-873A-C1BA6A30E979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAD9163-F785-45FF-8BB3-85EE14707A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2697,7 +2697,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2">
         <v>31</v>
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="C31" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2">
         <v>45</v>

--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAD9163-F785-45FF-8BB3-85EE14707A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD25CF18-D513-7245-9736-FD32FB0DE6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2086,10 +2086,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2378,18 +2374,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F231"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
-    <col min="1" max="1" width="15" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="53" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="3"/>
+    <col min="1" max="1" width="14.99609375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.7265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="53.04296875" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2409,7 +2405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2429,7 +2425,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -2437,10 +2433,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
+        <v>81</v>
+      </c>
+      <c r="D3" s="2">
         <v>80</v>
-      </c>
-      <c r="D3" s="2">
-        <v>79</v>
       </c>
       <c r="E3" s="2">
         <v>48</v>
@@ -2449,7 +2445,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2469,7 +2465,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2489,7 +2485,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2509,7 +2505,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2529,7 +2525,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2549,7 +2545,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2557,10 +2553,10 @@
         <v>14</v>
       </c>
       <c r="C9" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2">
         <v>50</v>
@@ -2569,7 +2565,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -2589,7 +2585,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -2609,7 +2605,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2629,7 +2625,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -2649,7 +2645,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2669,7 +2665,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -2689,7 +2685,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -2709,7 +2705,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
@@ -2729,7 +2725,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -2749,7 +2745,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A19" s="2" t="s">
         <v>328</v>
       </c>
@@ -2769,7 +2765,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2789,7 +2785,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -2809,7 +2805,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -2829,7 +2825,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -2849,7 +2845,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -2869,7 +2865,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -2889,7 +2885,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -2909,7 +2905,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -2929,7 +2925,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -2949,7 +2945,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -2969,7 +2965,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
@@ -2980,7 +2976,7 @@
         <v>65</v>
       </c>
       <c r="D30" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2">
         <v>28</v>
@@ -2989,7 +2985,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A31" s="2" t="s">
         <v>75</v>
       </c>
@@ -3009,7 +3005,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -3029,7 +3025,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -3049,7 +3045,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -3069,7 +3065,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -3089,7 +3085,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
@@ -3109,7 +3105,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
@@ -3129,7 +3125,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A38" s="2" t="s">
         <v>66</v>
       </c>
@@ -3149,7 +3145,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
@@ -3169,7 +3165,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A40" s="2" t="s">
         <v>73</v>
       </c>
@@ -3189,7 +3185,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A41" s="2" t="s">
         <v>74</v>
       </c>
@@ -3209,7 +3205,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A42" s="2" t="s">
         <v>91</v>
       </c>
@@ -3229,7 +3225,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
@@ -3237,10 +3233,10 @@
         <v>39</v>
       </c>
       <c r="C43" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2">
         <v>73</v>
@@ -3249,7 +3245,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -3269,7 +3265,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A45" s="2" t="s">
         <v>59</v>
       </c>
@@ -3289,7 +3285,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -3309,7 +3305,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -3320,7 +3316,7 @@
         <v>61</v>
       </c>
       <c r="D47" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2">
         <v>50</v>
@@ -3329,7 +3325,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A48" s="2" t="s">
         <v>60</v>
       </c>
@@ -3349,7 +3345,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A49" s="2" t="s">
         <v>62</v>
       </c>
@@ -3369,7 +3365,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A50" s="2" t="s">
         <v>63</v>
       </c>
@@ -3389,7 +3385,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A51" s="2" t="s">
         <v>72</v>
       </c>
@@ -3409,7 +3405,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A52" s="2" t="s">
         <v>81</v>
       </c>
@@ -3429,7 +3425,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A53" s="2" t="s">
         <v>96</v>
       </c>
@@ -3449,7 +3445,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -3469,7 +3465,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A55" s="2" t="s">
         <v>71</v>
       </c>
@@ -3489,7 +3485,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A56" s="2" t="s">
         <v>76</v>
       </c>
@@ -3509,7 +3505,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A57" s="2" t="s">
         <v>77</v>
       </c>
@@ -3529,7 +3525,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A58" s="2" t="s">
         <v>83</v>
       </c>
@@ -3537,10 +3533,10 @@
         <v>39</v>
       </c>
       <c r="C58" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D58" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E58" s="2">
         <v>46</v>
@@ -3549,7 +3545,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A59" s="2" t="s">
         <v>84</v>
       </c>
@@ -3569,7 +3565,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A60" s="2" t="s">
         <v>89</v>
       </c>
@@ -3589,7 +3585,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A61" s="2" t="s">
         <v>97</v>
       </c>
@@ -3609,7 +3605,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A62" s="2" t="s">
         <v>98</v>
       </c>
@@ -3629,7 +3625,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A63" s="2" t="s">
         <v>127</v>
       </c>
@@ -3649,7 +3645,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A64" s="2" t="s">
         <v>140</v>
       </c>
@@ -3669,7 +3665,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A65" s="2" t="s">
         <v>142</v>
       </c>
@@ -3689,7 +3685,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
@@ -3709,7 +3705,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A67" s="2" t="s">
         <v>87</v>
       </c>
@@ -3729,7 +3725,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A68" s="2" t="s">
         <v>92</v>
       </c>
@@ -3749,7 +3745,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A69" s="2" t="s">
         <v>94</v>
       </c>
@@ -3769,7 +3765,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A70" s="2" t="s">
         <v>79</v>
       </c>
@@ -3789,7 +3785,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A71" s="2" t="s">
         <v>99</v>
       </c>
@@ -3809,7 +3805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A72" s="2" t="s">
         <v>114</v>
       </c>
@@ -3829,7 +3825,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A73" s="2" t="s">
         <v>126</v>
       </c>
@@ -3849,7 +3845,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A74" s="2" t="s">
         <v>103</v>
       </c>
@@ -3869,7 +3865,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A75" s="2" t="s">
         <v>108</v>
       </c>
@@ -3889,7 +3885,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A76" s="2" t="s">
         <v>106</v>
       </c>
@@ -3909,7 +3905,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A77" s="2" t="s">
         <v>122</v>
       </c>
@@ -3929,7 +3925,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A78" s="2" t="s">
         <v>136</v>
       </c>
@@ -3949,7 +3945,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A79" s="2" t="s">
         <v>86</v>
       </c>
@@ -3969,7 +3965,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A80" s="2" t="s">
         <v>109</v>
       </c>
@@ -3989,7 +3985,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A81" s="2" t="s">
         <v>111</v>
       </c>
@@ -4009,7 +4005,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A82" s="2" t="s">
         <v>113</v>
       </c>
@@ -4029,7 +4025,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A83" s="2" t="s">
         <v>196</v>
       </c>
@@ -4049,7 +4045,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A84" s="2" t="s">
         <v>131</v>
       </c>
@@ -4069,7 +4065,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A85" s="2" t="s">
         <v>149</v>
       </c>
@@ -4089,7 +4085,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A86" s="2" t="s">
         <v>105</v>
       </c>
@@ -4109,7 +4105,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A87" s="2" t="s">
         <v>115</v>
       </c>
@@ -4129,7 +4125,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A88" s="2" t="s">
         <v>116</v>
       </c>
@@ -4149,7 +4145,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A89" s="2" t="s">
         <v>129</v>
       </c>
@@ -4169,7 +4165,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A90" s="2" t="s">
         <v>133</v>
       </c>
@@ -4189,7 +4185,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A91" s="2" t="s">
         <v>138</v>
       </c>
@@ -4209,7 +4205,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A92" s="2" t="s">
         <v>160</v>
       </c>
@@ -4229,7 +4225,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A93" s="2" t="s">
         <v>102</v>
       </c>
@@ -4249,7 +4245,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A94" s="2" t="s">
         <v>118</v>
       </c>
@@ -4269,7 +4265,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A95" s="2" t="s">
         <v>123</v>
       </c>
@@ -4289,7 +4285,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A96" s="2" t="s">
         <v>141</v>
       </c>
@@ -4309,7 +4305,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A97" s="2" t="s">
         <v>168</v>
       </c>
@@ -4329,7 +4325,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A98" s="2" t="s">
         <v>218</v>
       </c>
@@ -4349,7 +4345,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A99" s="2" t="s">
         <v>104</v>
       </c>
@@ -4369,7 +4365,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A100" s="2" t="s">
         <v>117</v>
       </c>
@@ -4389,7 +4385,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A101" s="2" t="s">
         <v>150</v>
       </c>
@@ -4409,7 +4405,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A102" s="2" t="s">
         <v>192</v>
       </c>
@@ -4429,7 +4425,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A103" s="2" t="s">
         <v>199</v>
       </c>
@@ -4449,7 +4445,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A104" s="2" t="s">
         <v>205</v>
       </c>
@@ -4469,7 +4465,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A105" s="2" t="s">
         <v>101</v>
       </c>
@@ -4489,7 +4485,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A106" s="2" t="s">
         <v>121</v>
       </c>
@@ -4509,7 +4505,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A107" s="2" t="s">
         <v>125</v>
       </c>
@@ -4529,7 +4525,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A108" s="2" t="s">
         <v>128</v>
       </c>
@@ -4549,7 +4545,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A109" s="2" t="s">
         <v>144</v>
       </c>
@@ -4569,7 +4565,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A110" s="2" t="s">
         <v>147</v>
       </c>
@@ -4589,7 +4585,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A111" s="2" t="s">
         <v>164</v>
       </c>
@@ -4609,7 +4605,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A112" s="2" t="s">
         <v>171</v>
       </c>
@@ -4629,7 +4625,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -4649,7 +4645,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A114" s="2" t="s">
         <v>112</v>
       </c>
@@ -4669,7 +4665,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A115" s="2" t="s">
         <v>119</v>
       </c>
@@ -4689,7 +4685,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A116" s="2" t="s">
         <v>130</v>
       </c>
@@ -4709,7 +4705,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A117" s="2" t="s">
         <v>135</v>
       </c>
@@ -4729,7 +4725,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A118" s="2" t="s">
         <v>157</v>
       </c>
@@ -4749,7 +4745,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A119" s="2" t="s">
         <v>163</v>
       </c>
@@ -4769,7 +4765,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A120" s="2" t="s">
         <v>159</v>
       </c>
@@ -4789,7 +4785,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A121" s="2" t="s">
         <v>167</v>
       </c>
@@ -4809,7 +4805,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A122" s="2" t="s">
         <v>185</v>
       </c>
@@ -4829,7 +4825,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A123" s="2" t="s">
         <v>224</v>
       </c>
@@ -4849,7 +4845,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A124" s="2" t="s">
         <v>227</v>
       </c>
@@ -4869,7 +4865,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A125" s="2" t="s">
         <v>124</v>
       </c>
@@ -4889,7 +4885,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A126" s="2" t="s">
         <v>151</v>
       </c>
@@ -4909,7 +4905,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A127" s="2" t="s">
         <v>156</v>
       </c>
@@ -4929,7 +4925,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A128" s="2" t="s">
         <v>165</v>
       </c>
@@ -4949,7 +4945,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A129" s="2" t="s">
         <v>179</v>
       </c>
@@ -4969,7 +4965,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A130" s="2" t="s">
         <v>181</v>
       </c>
@@ -4989,7 +4985,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A131" s="2" t="s">
         <v>188</v>
       </c>
@@ -5009,7 +5005,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A132" s="2" t="s">
         <v>216</v>
       </c>
@@ -5029,7 +5025,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -5049,7 +5045,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A134" s="2" t="s">
         <v>172</v>
       </c>
@@ -5069,7 +5065,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A135" s="2" t="s">
         <v>175</v>
       </c>
@@ -5089,7 +5085,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A136" s="2" t="s">
         <v>182</v>
       </c>
@@ -5109,7 +5105,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A137" s="2" t="s">
         <v>241</v>
       </c>
@@ -5129,7 +5125,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A138" s="2" t="s">
         <v>146</v>
       </c>
@@ -5149,7 +5145,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A139" s="2" t="s">
         <v>152</v>
       </c>
@@ -5169,7 +5165,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A140" s="2" t="s">
         <v>177</v>
       </c>
@@ -5189,7 +5185,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A141" s="2" t="s">
         <v>186</v>
       </c>
@@ -5209,7 +5205,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A142" s="2" t="s">
         <v>203</v>
       </c>
@@ -5229,7 +5225,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A143" s="2" t="s">
         <v>184</v>
       </c>
@@ -5249,7 +5245,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A144" s="2" t="s">
         <v>190</v>
       </c>
@@ -5269,7 +5265,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A145" s="2" t="s">
         <v>198</v>
       </c>
@@ -5289,7 +5285,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A146" s="2" t="s">
         <v>206</v>
       </c>
@@ -5309,7 +5305,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A147" s="2" t="s">
         <v>213</v>
       </c>
@@ -5329,7 +5325,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A148" s="2" t="s">
         <v>215</v>
       </c>
@@ -5349,7 +5345,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A149" s="2" t="s">
         <v>162</v>
       </c>
@@ -5369,7 +5365,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A150" s="2" t="s">
         <v>174</v>
       </c>
@@ -5389,7 +5385,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A151" s="2" t="s">
         <v>195</v>
       </c>
@@ -5409,7 +5405,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A152" s="2" t="s">
         <v>197</v>
       </c>
@@ -5429,7 +5425,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A153" s="2" t="s">
         <v>208</v>
       </c>
@@ -5449,7 +5445,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A154" s="2" t="s">
         <v>225</v>
       </c>
@@ -5469,7 +5465,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A155" s="2" t="s">
         <v>243</v>
       </c>
@@ -5489,7 +5485,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A156" s="2" t="s">
         <v>154</v>
       </c>
@@ -5509,7 +5505,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A157" s="2" t="s">
         <v>169</v>
       </c>
@@ -5529,7 +5525,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A158" s="2" t="s">
         <v>193</v>
       </c>
@@ -5549,7 +5545,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A159" s="2" t="s">
         <v>207</v>
       </c>
@@ -5569,7 +5565,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A160" s="2" t="s">
         <v>239</v>
       </c>
@@ -5589,7 +5585,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A161" s="2" t="s">
         <v>212</v>
       </c>
@@ -5609,7 +5605,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A162" s="2" t="s">
         <v>228</v>
       </c>
@@ -5629,7 +5625,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A163" s="2" t="s">
         <v>231</v>
       </c>
@@ -5649,7 +5645,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A164" s="2" t="s">
         <v>201</v>
       </c>
@@ -5669,7 +5665,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A165" s="2" t="s">
         <v>220</v>
       </c>
@@ -5689,7 +5685,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A166" s="2" t="s">
         <v>223</v>
       </c>
@@ -5709,7 +5705,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A167" s="2" t="s">
         <v>236</v>
       </c>
@@ -5729,7 +5725,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A168" s="2" t="s">
         <v>232</v>
       </c>
@@ -5749,7 +5745,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A169" s="2" t="s">
         <v>234</v>
       </c>
@@ -5769,7 +5765,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A170" s="2" t="s">
         <v>323</v>
       </c>
@@ -5789,7 +5785,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A171" s="2" t="s">
         <v>226</v>
       </c>
@@ -5809,7 +5805,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A172" s="2" t="s">
         <v>221</v>
       </c>
@@ -5829,7 +5825,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A173" s="2" t="s">
         <v>238</v>
       </c>
@@ -5849,7 +5845,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A174" s="2" t="s">
         <v>240</v>
       </c>
@@ -5869,7 +5865,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A175" s="2" t="s">
         <v>244</v>
       </c>
@@ -5889,7 +5885,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A176" s="2" t="s">
         <v>245</v>
       </c>
@@ -5909,7 +5905,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A177" s="2" t="s">
         <v>229</v>
       </c>
@@ -5929,7 +5925,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A178" s="3" t="s">
         <v>268</v>
       </c>
@@ -5949,7 +5945,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A179" s="3" t="s">
         <v>365</v>
       </c>
@@ -5969,7 +5965,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A180" s="3" t="s">
         <v>368</v>
       </c>
@@ -5989,7 +5985,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A181" s="3" t="s">
         <v>371</v>
       </c>
@@ -6009,7 +6005,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A182" s="3" t="s">
         <v>373</v>
       </c>
@@ -6029,7 +6025,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A183" s="3" t="s">
         <v>375</v>
       </c>
@@ -6049,7 +6045,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A184" s="3" t="s">
         <v>377</v>
       </c>
@@ -6069,7 +6065,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A185" s="3" t="s">
         <v>379</v>
       </c>
@@ -6089,7 +6085,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A186" s="3" t="s">
         <v>381</v>
       </c>
@@ -6109,7 +6105,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A187" s="3" t="s">
         <v>383</v>
       </c>
@@ -6129,7 +6125,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A188" s="3" t="s">
         <v>385</v>
       </c>
@@ -6149,7 +6145,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A189" s="3" t="s">
         <v>388</v>
       </c>
@@ -6169,7 +6165,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A190" s="3" t="s">
         <v>390</v>
       </c>
@@ -6189,7 +6185,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A191" s="3" t="s">
         <v>392</v>
       </c>
@@ -6209,7 +6205,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A192" s="3" t="s">
         <v>394</v>
       </c>
@@ -6229,7 +6225,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A193" s="3" t="s">
         <v>396</v>
       </c>
@@ -6249,7 +6245,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A194" s="3" t="s">
         <v>398</v>
       </c>
@@ -6269,7 +6265,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A195" s="3" t="s">
         <v>401</v>
       </c>
@@ -6289,7 +6285,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A196" s="3" t="s">
         <v>403</v>
       </c>
@@ -6309,7 +6305,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A197" s="3" t="s">
         <v>405</v>
       </c>
@@ -6329,7 +6325,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A198" s="3" t="s">
         <v>407</v>
       </c>
@@ -6349,7 +6345,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A199" s="3" t="s">
         <v>409</v>
       </c>
@@ -6369,7 +6365,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A200" s="3" t="s">
         <v>410</v>
       </c>
@@ -6389,7 +6385,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A201" s="3" t="s">
         <v>415</v>
       </c>
@@ -6409,7 +6405,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A202" s="3" t="s">
         <v>417</v>
       </c>
@@ -6429,7 +6425,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A203" s="3" t="s">
         <v>420</v>
       </c>
@@ -6449,7 +6445,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A204" s="3" t="s">
         <v>422</v>
       </c>
@@ -6469,7 +6465,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A205" s="3" t="s">
         <v>424</v>
       </c>
@@ -6489,7 +6485,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A206" s="3" t="s">
         <v>429</v>
       </c>
@@ -6509,7 +6505,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A207" s="3" t="s">
         <v>432</v>
       </c>
@@ -6529,7 +6525,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A208" s="3" t="s">
         <v>434</v>
       </c>
@@ -6549,7 +6545,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A209" s="3" t="s">
         <v>436</v>
       </c>
@@ -6569,7 +6565,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A210" s="3" t="s">
         <v>438</v>
       </c>
@@ -6589,7 +6585,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A211" s="3" t="s">
         <v>441</v>
       </c>
@@ -6609,7 +6605,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A212" s="3" t="s">
         <v>443</v>
       </c>
@@ -6629,7 +6625,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A213" s="3" t="s">
         <v>445</v>
       </c>
@@ -6649,7 +6645,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A214" s="3" t="s">
         <v>447</v>
       </c>
@@ -6669,7 +6665,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A215" s="3" t="s">
         <v>450</v>
       </c>
@@ -6689,7 +6685,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A216" s="3" t="s">
         <v>452</v>
       </c>
@@ -6709,7 +6705,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A217" s="3" t="s">
         <v>454</v>
       </c>
@@ -6729,7 +6725,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A218" s="3" t="s">
         <v>456</v>
       </c>
@@ -6749,7 +6745,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A219" s="3" t="s">
         <v>459</v>
       </c>
@@ -6769,7 +6765,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A220" s="3" t="s">
         <v>461</v>
       </c>
@@ -6789,7 +6785,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A221" s="3" t="s">
         <v>463</v>
       </c>
@@ -6809,7 +6805,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A222" s="3" t="s">
         <v>465</v>
       </c>
@@ -6829,7 +6825,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A223" s="3" t="s">
         <v>468</v>
       </c>
@@ -6849,7 +6845,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A224" s="3" t="s">
         <v>470</v>
       </c>
@@ -6869,7 +6865,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A225" s="3" t="s">
         <v>472</v>
       </c>
@@ -6889,7 +6885,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A226" s="3" t="s">
         <v>474</v>
       </c>
@@ -6909,7 +6905,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A227" s="3" t="s">
         <v>476</v>
       </c>
@@ -6929,7 +6925,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A228" s="3" t="s">
         <v>477</v>
       </c>
@@ -6949,7 +6945,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A229" s="3" t="s">
         <v>478</v>
       </c>
@@ -6969,7 +6965,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A230" s="3" t="s">
         <v>479</v>
       </c>
@@ -6989,7 +6985,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A231" s="3" t="s">
         <v>480</v>
       </c>
@@ -7017,23 +7013,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B56F6E2A19A2F74190C4E1D46B40D305" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="41a44f59d3b68d1f18012b98926b6f28">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xmlns:ns4="1212b74f-52fc-4973-8f22-7750ea9e0eb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e80f7c3813526ed05737851d7f7b407" ns3:_="" ns4:_="">
     <xsd:import namespace="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
@@ -7228,32 +7207,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6C3AB4F-6546-4A10-9B21-424D4E5F957B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7262,13 +7233,25 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
     <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
+  <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD25CF18-D513-7245-9736-FD32FB0DE6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8187B47-4771-6F40-984C-9391848036AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2413,7 +2413,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2">
         <v>84</v>

--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8187B47-4771-6F40-984C-9391848036AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A8C4448-402C-2E49-927D-F51428A20750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="491">
   <si>
     <t>選手名</t>
   </si>
@@ -318,9 +318,6 @@
   </si>
   <si>
     <t>C:82</t>
-  </si>
-  <si>
-    <t>宮崎敏郎</t>
   </si>
   <si>
     <t>3B:48</t>
@@ -1989,6 +1986,9 @@
   <si>
     <t>2B:48 / 3B:53 / SS:38 / CF:55 / RF:44</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮﨑敏郎</t>
   </si>
 </sst>
 </file>
@@ -2373,6 +2373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F231"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
@@ -2405,7 +2406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2422,10 +2423,10 @@
         <v>66</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -2442,10 +2443,10 @@
         <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2462,10 +2463,10 @@
         <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2482,10 +2483,10 @@
         <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2502,10 +2503,10 @@
         <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2522,10 +2523,10 @@
         <v>56</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2545,7 +2546,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2562,10 +2563,10 @@
         <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -2582,10 +2583,10 @@
         <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -2602,10 +2603,10 @@
         <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2622,10 +2623,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -2642,10 +2643,10 @@
         <v>34</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2662,10 +2663,10 @@
         <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -2682,10 +2683,10 @@
         <v>78</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -2702,7 +2703,7 @@
         <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.1">
@@ -2722,7 +2723,7 @@
         <v>61</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.1">
@@ -2742,12 +2743,12 @@
         <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A19" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>39</v>
@@ -2762,10 +2763,10 @@
         <v>72</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.1">
@@ -2802,10 +2803,10 @@
         <v>32</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.1">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -2822,10 +2823,10 @@
         <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -2845,7 +2846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -2862,10 +2863,10 @@
         <v>55</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -2882,10 +2883,10 @@
         <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -2902,10 +2903,10 @@
         <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -2922,10 +2923,10 @@
         <v>70</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -2942,10 +2943,10 @@
         <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -2962,10 +2963,10 @@
         <v>37</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
@@ -2985,7 +2986,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A31" s="2" t="s">
         <v>75</v>
       </c>
@@ -3002,10 +3003,10 @@
         <v>77</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -3042,10 +3043,10 @@
         <v>62</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -3062,10 +3063,10 @@
         <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -3082,10 +3083,10 @@
         <v>58</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
@@ -3102,10 +3103,10 @@
         <v>79</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A38" s="2" t="s">
         <v>66</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
@@ -3162,7 +3163,7 @@
         <v>60</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.1">
@@ -3182,10 +3183,10 @@
         <v>61</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A41" s="2" t="s">
         <v>74</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>21</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.1">
@@ -3222,10 +3223,10 @@
         <v>32</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
@@ -3245,7 +3246,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -3262,10 +3263,10 @@
         <v>55</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A45" s="2" t="s">
         <v>59</v>
       </c>
@@ -3282,10 +3283,10 @@
         <v>52</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -3302,10 +3303,10 @@
         <v>40</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A48" s="2" t="s">
         <v>60</v>
       </c>
@@ -3342,10 +3343,10 @@
         <v>42</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A49" s="2" t="s">
         <v>62</v>
       </c>
@@ -3362,10 +3363,10 @@
         <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A50" s="2" t="s">
         <v>63</v>
       </c>
@@ -3382,10 +3383,10 @@
         <v>33</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A51" s="2" t="s">
         <v>72</v>
       </c>
@@ -3402,10 +3403,10 @@
         <v>60</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A52" s="2" t="s">
         <v>81</v>
       </c>
@@ -3425,9 +3426,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A53" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>33</v>
@@ -3442,12 +3443,12 @@
         <v>24</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A54" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>41</v>
@@ -3462,10 +3463,10 @@
         <v>80</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A55" s="2" t="s">
         <v>71</v>
       </c>
@@ -3482,10 +3483,10 @@
         <v>48</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A56" s="2" t="s">
         <v>76</v>
       </c>
@@ -3502,10 +3503,10 @@
         <v>45</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A57" s="2" t="s">
         <v>77</v>
       </c>
@@ -3525,7 +3526,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A58" s="2" t="s">
         <v>83</v>
       </c>
@@ -3542,10 +3543,10 @@
         <v>46</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A59" s="2" t="s">
         <v>84</v>
       </c>
@@ -3562,10 +3563,10 @@
         <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A60" s="2" t="s">
         <v>89</v>
       </c>
@@ -3585,9 +3586,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A61" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
@@ -3602,12 +3603,12 @@
         <v>34</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.1">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A62" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>9</v>
@@ -3622,12 +3623,12 @@
         <v>47</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A63" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>27</v>
@@ -3642,12 +3643,12 @@
         <v>30</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>27</v>
@@ -3662,12 +3663,12 @@
         <v>66</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A65" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>39</v>
@@ -3682,10 +3683,10 @@
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
@@ -3702,10 +3703,10 @@
         <v>90</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A67" s="2" t="s">
         <v>87</v>
       </c>
@@ -3725,7 +3726,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A68" s="2" t="s">
         <v>92</v>
       </c>
@@ -3742,12 +3743,12 @@
         <v>34</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A69" s="2" t="s">
-        <v>94</v>
+        <v>489</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>29</v>
@@ -3762,10 +3763,10 @@
         <v>30</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A70" s="2" t="s">
         <v>79</v>
       </c>
@@ -3787,7 +3788,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A71" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>29</v>
@@ -3802,12 +3803,12 @@
         <v>62</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A72" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>39</v>
@@ -3822,12 +3823,12 @@
         <v>66</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A73" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>29</v>
@@ -3845,9 +3846,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A74" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>41</v>
@@ -3862,12 +3863,12 @@
         <v>53</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A75" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>39</v>
@@ -3882,12 +3883,12 @@
         <v>30</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A76" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>9</v>
@@ -3902,12 +3903,12 @@
         <v>55</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A77" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>14</v>
@@ -3922,12 +3923,12 @@
         <v>58</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A78" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -3942,10 +3943,10 @@
         <v>42</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A79" s="2" t="s">
         <v>86</v>
       </c>
@@ -3962,12 +3963,12 @@
         <v>41</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A80" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>41</v>
@@ -3982,12 +3983,12 @@
         <v>60</v>
       </c>
       <c r="F80" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A81" s="2" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A81" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>43</v>
@@ -4002,12 +4003,12 @@
         <v>26</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A82" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>29</v>
@@ -4025,9 +4026,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A83" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>49</v>
@@ -4042,12 +4043,12 @@
         <v>40</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A84" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>11</v>
@@ -4062,12 +4063,12 @@
         <v>46</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A85" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>43</v>
@@ -4082,12 +4083,12 @@
         <v>52</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A86" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>49</v>
@@ -4102,12 +4103,12 @@
         <v>78</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A87" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>43</v>
@@ -4122,12 +4123,12 @@
         <v>71</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A88" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>7</v>
@@ -4142,12 +4143,12 @@
         <v>77</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A89" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>14</v>
@@ -4162,12 +4163,12 @@
         <v>85</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A90" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>9</v>
@@ -4182,12 +4183,12 @@
         <v>58</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A91" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>29</v>
@@ -4202,12 +4203,12 @@
         <v>54</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A92" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>14</v>
@@ -4222,12 +4223,12 @@
         <v>48</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A93" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
@@ -4242,12 +4243,12 @@
         <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A94" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>27</v>
@@ -4262,12 +4263,12 @@
         <v>30</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A95" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>27</v>
@@ -4282,12 +4283,12 @@
         <v>34</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A96" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>49</v>
@@ -4302,12 +4303,12 @@
         <v>71</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.1">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A97" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>9</v>
@@ -4322,12 +4323,12 @@
         <v>29</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A98" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>9</v>
@@ -4342,12 +4343,12 @@
         <v>41</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>43</v>
@@ -4362,12 +4363,12 @@
         <v>36</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A100" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>49</v>
@@ -4382,12 +4383,12 @@
         <v>27</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A101" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>11</v>
@@ -4402,12 +4403,12 @@
         <v>77</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A102" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>7</v>
@@ -4422,12 +4423,12 @@
         <v>53</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A103" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>41</v>
@@ -4442,12 +4443,12 @@
         <v>66</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A104" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>49</v>
@@ -4462,12 +4463,12 @@
         <v>41</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A105" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>43</v>
@@ -4482,12 +4483,12 @@
         <v>73</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A106" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>16</v>
@@ -4502,12 +4503,12 @@
         <v>77</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A107" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>41</v>
@@ -4522,12 +4523,12 @@
         <v>58</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A108" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>39</v>
@@ -4542,12 +4543,12 @@
         <v>71</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A109" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>39</v>
@@ -4562,12 +4563,12 @@
         <v>30</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A110" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>39</v>
@@ -4582,12 +4583,12 @@
         <v>71</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A111" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>7</v>
@@ -4602,12 +4603,12 @@
         <v>31</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A112" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -4622,12 +4623,12 @@
         <v>30</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A113" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>33</v>
@@ -4642,12 +4643,12 @@
         <v>30</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A114" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>39</v>
@@ -4662,12 +4663,12 @@
         <v>66</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A115" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>11</v>
@@ -4682,12 +4683,12 @@
         <v>25</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A116" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>41</v>
@@ -4702,12 +4703,12 @@
         <v>28</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.1">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A117" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
@@ -4722,12 +4723,12 @@
         <v>71</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A118" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>33</v>
@@ -4742,12 +4743,12 @@
         <v>30</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A119" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>49</v>
@@ -4762,12 +4763,12 @@
         <v>60</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A120" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>9</v>
@@ -4782,12 +4783,12 @@
         <v>56</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.1">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A121" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>39</v>
@@ -4802,12 +4803,12 @@
         <v>75</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A122" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
@@ -4822,12 +4823,12 @@
         <v>82</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A123" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>9</v>
@@ -4842,12 +4843,12 @@
         <v>78</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A124" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>33</v>
@@ -4862,12 +4863,12 @@
         <v>41</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A125" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>16</v>
@@ -4882,12 +4883,12 @@
         <v>58</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A126" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>39</v>
@@ -4902,12 +4903,12 @@
         <v>58</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A127" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>43</v>
@@ -4922,12 +4923,12 @@
         <v>30</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A128" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>49</v>
@@ -4942,12 +4943,12 @@
         <v>34</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A129" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>33</v>
@@ -4962,12 +4963,12 @@
         <v>66</v>
       </c>
       <c r="F129" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A130" s="2" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A130" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>16</v>
@@ -4982,12 +4983,12 @@
         <v>70</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A131" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>14</v>
@@ -5002,12 +5003,12 @@
         <v>67</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A132" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>33</v>
@@ -5022,12 +5023,12 @@
         <v>55</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A133" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>9</v>
@@ -5042,12 +5043,12 @@
         <v>70</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A134" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>33</v>
@@ -5062,12 +5063,12 @@
         <v>37</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A135" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>29</v>
@@ -5082,12 +5083,12 @@
         <v>72</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A136" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>29</v>
@@ -5102,12 +5103,12 @@
         <v>80</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A137" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>43</v>
@@ -5122,12 +5123,12 @@
         <v>72</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A138" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>7</v>
@@ -5145,9 +5146,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A139" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>27</v>
@@ -5162,12 +5163,12 @@
         <v>30</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A140" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>16</v>
@@ -5182,12 +5183,12 @@
         <v>48</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.1">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A141" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>27</v>
@@ -5202,12 +5203,12 @@
         <v>72</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A142" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>29</v>
@@ -5222,12 +5223,12 @@
         <v>28</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A143" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>14</v>
@@ -5242,12 +5243,12 @@
         <v>69</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A144" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>7</v>
@@ -5262,12 +5263,12 @@
         <v>46</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A145" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>9</v>
@@ -5282,12 +5283,12 @@
         <v>30</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A146" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>49</v>
@@ -5302,12 +5303,12 @@
         <v>49</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A147" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>9</v>
@@ -5322,12 +5323,12 @@
         <v>94</v>
       </c>
       <c r="F147" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A148" s="2" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A148" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>43</v>
@@ -5342,12 +5343,12 @@
         <v>61</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A149" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>14</v>
@@ -5362,12 +5363,12 @@
         <v>30</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A150" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>7</v>
@@ -5382,12 +5383,12 @@
         <v>76</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A151" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>14</v>
@@ -5402,12 +5403,12 @@
         <v>21</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A152" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>11</v>
@@ -5422,12 +5423,12 @@
         <v>69</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A153" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>29</v>
@@ -5442,12 +5443,12 @@
         <v>71</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A154" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>7</v>
@@ -5462,12 +5463,12 @@
         <v>26</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A155" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>27</v>
@@ -5482,12 +5483,12 @@
         <v>44</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A156" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>49</v>
@@ -5502,12 +5503,12 @@
         <v>30</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A157" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>43</v>
@@ -5522,12 +5523,12 @@
         <v>61</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A158" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>14</v>
@@ -5542,12 +5543,12 @@
         <v>56</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A159" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>16</v>
@@ -5562,12 +5563,12 @@
         <v>80</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A160" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>7</v>
@@ -5582,12 +5583,12 @@
         <v>70</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A161" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>27</v>
@@ -5602,12 +5603,12 @@
         <v>74</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A162" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>9</v>
@@ -5622,12 +5623,12 @@
         <v>78</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A163" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>11</v>
@@ -5642,12 +5643,12 @@
         <v>59</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A164" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>33</v>
@@ -5662,12 +5663,12 @@
         <v>71</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A165" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>16</v>
@@ -5682,12 +5683,12 @@
         <v>30</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A166" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>33</v>
@@ -5702,12 +5703,12 @@
         <v>52</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A167" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>43</v>
@@ -5722,12 +5723,12 @@
         <v>61</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.1">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A168" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>43</v>
@@ -5742,12 +5743,12 @@
         <v>32</v>
       </c>
       <c r="F168" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A169" s="2" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A169" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>16</v>
@@ -5762,12 +5763,12 @@
         <v>30</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A170" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>9</v>
@@ -5782,12 +5783,12 @@
         <v>71</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A171" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>7</v>
@@ -5802,12 +5803,12 @@
         <v>52</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A172" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>41</v>
@@ -5822,12 +5823,12 @@
         <v>40</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A173" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>41</v>
@@ -5842,12 +5843,12 @@
         <v>55</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A174" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>43</v>
@@ -5862,12 +5863,12 @@
         <v>66</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A175" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>16</v>
@@ -5882,12 +5883,12 @@
         <v>30</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A176" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>16</v>
@@ -5902,12 +5903,12 @@
         <v>45</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A177" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>11</v>
@@ -5922,12 +5923,12 @@
         <v>30</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A178" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>43</v>
@@ -5942,15 +5943,15 @@
         <v>95</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A179" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B179" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="C179" s="3">
         <v>42</v>
@@ -5962,15 +5963,15 @@
         <v>69</v>
       </c>
       <c r="F179" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A180" s="3" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A180" s="3" t="s">
+      <c r="B180" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="C180" s="3">
         <v>39</v>
@@ -5982,15 +5983,15 @@
         <v>82</v>
       </c>
       <c r="F180" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A181" s="3" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A181" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="B181" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C181" s="3">
         <v>18</v>
@@ -6002,15 +6003,15 @@
         <v>28</v>
       </c>
       <c r="F181" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A182" s="3" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A182" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="B182" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C182" s="3">
         <v>33</v>
@@ -6022,15 +6023,15 @@
         <v>37</v>
       </c>
       <c r="F182" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A183" s="3" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A183" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="B183" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C183" s="3">
         <v>31</v>
@@ -6042,15 +6043,15 @@
         <v>51</v>
       </c>
       <c r="F183" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A184" s="3" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A184" s="3" t="s">
-        <v>377</v>
-      </c>
       <c r="B184" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C184" s="3">
         <v>38</v>
@@ -6062,15 +6063,15 @@
         <v>69</v>
       </c>
       <c r="F184" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A185" s="3" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A185" s="3" t="s">
-        <v>379</v>
-      </c>
       <c r="B185" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C185" s="3">
         <v>31</v>
@@ -6082,15 +6083,15 @@
         <v>46</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A186" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B186" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="C186" s="3">
         <v>44</v>
@@ -6102,15 +6103,15 @@
         <v>25</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A187" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C187" s="3">
         <v>39</v>
@@ -6122,15 +6123,15 @@
         <v>68</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A188" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C188" s="3">
         <v>57</v>
@@ -6142,15 +6143,15 @@
         <v>58</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A189" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C189" s="3">
         <v>42</v>
@@ -6162,15 +6163,15 @@
         <v>70</v>
       </c>
       <c r="F189" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A190" s="3" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A190" s="3" t="s">
+      <c r="B190" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="C190" s="3">
         <v>16</v>
@@ -6182,15 +6183,15 @@
         <v>54</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.1">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A191" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C191" s="3">
         <v>28</v>
@@ -6202,15 +6203,15 @@
         <v>66</v>
       </c>
       <c r="F191" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A192" s="3" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A192" s="3" t="s">
-        <v>394</v>
-      </c>
       <c r="B192" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C192" s="3">
         <v>52</v>
@@ -6222,15 +6223,15 @@
         <v>38</v>
       </c>
       <c r="F192" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A193" s="3" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A193" s="3" t="s">
-        <v>396</v>
-      </c>
       <c r="B193" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C193" s="3">
         <v>44</v>
@@ -6242,15 +6243,15 @@
         <v>61</v>
       </c>
       <c r="F193" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A194" s="3" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A194" s="3" t="s">
+      <c r="B194" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="C194" s="3">
         <v>39</v>
@@ -6262,15 +6263,15 @@
         <v>68</v>
       </c>
       <c r="F194" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A195" s="3" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A195" s="3" t="s">
-        <v>401</v>
-      </c>
       <c r="B195" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C195" s="3">
         <v>42</v>
@@ -6282,15 +6283,15 @@
         <v>64</v>
       </c>
       <c r="F195" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A196" s="3" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A196" s="3" t="s">
-        <v>403</v>
-      </c>
       <c r="B196" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C196" s="3">
         <v>50</v>
@@ -6302,15 +6303,15 @@
         <v>41</v>
       </c>
       <c r="F196" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A197" s="3" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A197" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="B197" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C197" s="3">
         <v>15</v>
@@ -6322,15 +6323,15 @@
         <v>28</v>
       </c>
       <c r="F197" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A198" s="3" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A198" s="3" t="s">
+      <c r="B198" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="C198" s="3">
         <v>41</v>
@@ -6342,15 +6343,15 @@
         <v>80</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A199" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C199" s="3">
         <v>54</v>
@@ -6362,15 +6363,15 @@
         <v>43</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A200" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C200" s="3">
         <v>57</v>
@@ -6382,15 +6383,15 @@
         <v>60</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A201" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C201" s="3">
         <v>49</v>
@@ -6402,15 +6403,15 @@
         <v>51</v>
       </c>
       <c r="F201" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A202" s="3" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A202" s="3" t="s">
+      <c r="B202" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="C202" s="3">
         <v>43</v>
@@ -6422,15 +6423,15 @@
         <v>59</v>
       </c>
       <c r="F202" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A203" s="3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A203" s="3" t="s">
-        <v>420</v>
-      </c>
       <c r="B203" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C203" s="3">
         <v>42</v>
@@ -6442,15 +6443,15 @@
         <v>63</v>
       </c>
       <c r="F203" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A204" s="3" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A204" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="B204" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C204" s="3">
         <v>46</v>
@@ -6462,15 +6463,15 @@
         <v>55</v>
       </c>
       <c r="F204" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A205" s="3" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A205" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="B205" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C205" s="3">
         <v>36</v>
@@ -6482,15 +6483,15 @@
         <v>41</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A206" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B206" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="C206" s="3">
         <v>37</v>
@@ -6502,15 +6503,15 @@
         <v>66</v>
       </c>
       <c r="F206" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A207" s="3" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A207" s="3" t="s">
-        <v>432</v>
-      </c>
       <c r="B207" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C207" s="3">
         <v>35</v>
@@ -6522,15 +6523,15 @@
         <v>51</v>
       </c>
       <c r="F207" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A208" s="3" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A208" s="3" t="s">
-        <v>434</v>
-      </c>
       <c r="B208" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C208" s="3">
         <v>41</v>
@@ -6542,15 +6543,15 @@
         <v>48</v>
       </c>
       <c r="F208" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A209" s="3" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A209" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="B209" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C209" s="3">
         <v>45</v>
@@ -6562,15 +6563,15 @@
         <v>79</v>
       </c>
       <c r="F209" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A210" s="3" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A210" s="3" t="s">
+      <c r="B210" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="C210" s="3">
         <v>59</v>
@@ -6582,15 +6583,15 @@
         <v>44</v>
       </c>
       <c r="F210" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A211" s="3" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A211" s="3" t="s">
-        <v>441</v>
-      </c>
       <c r="B211" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C211" s="3">
         <v>46</v>
@@ -6602,15 +6603,15 @@
         <v>22</v>
       </c>
       <c r="F211" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A212" s="3" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A212" s="3" t="s">
-        <v>443</v>
-      </c>
       <c r="B212" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C212" s="3">
         <v>57</v>
@@ -6622,15 +6623,15 @@
         <v>41</v>
       </c>
       <c r="F212" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A213" s="3" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A213" s="3" t="s">
-        <v>445</v>
-      </c>
       <c r="B213" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C213" s="3">
         <v>36</v>
@@ -6642,15 +6643,15 @@
         <v>55</v>
       </c>
       <c r="F213" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A214" s="3" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A214" s="3" t="s">
+      <c r="B214" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="C214" s="3">
         <v>38</v>
@@ -6662,15 +6663,15 @@
         <v>57</v>
       </c>
       <c r="F214" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A215" s="3" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A215" s="3" t="s">
-        <v>450</v>
-      </c>
       <c r="B215" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C215" s="3">
         <v>42</v>
@@ -6682,15 +6683,15 @@
         <v>66</v>
       </c>
       <c r="F215" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A216" s="3" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A216" s="3" t="s">
-        <v>452</v>
-      </c>
       <c r="B216" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C216" s="3">
         <v>41</v>
@@ -6702,15 +6703,15 @@
         <v>91</v>
       </c>
       <c r="F216" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A217" s="3" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A217" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="B217" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C217" s="3">
         <v>28</v>
@@ -6722,15 +6723,15 @@
         <v>80</v>
       </c>
       <c r="F217" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A218" s="3" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A218" s="3" t="s">
+      <c r="B218" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="C218" s="3">
         <v>51</v>
@@ -6742,15 +6743,15 @@
         <v>48</v>
       </c>
       <c r="F218" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A219" s="3" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A219" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="B219" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C219" s="3">
         <v>29</v>
@@ -6762,15 +6763,15 @@
         <v>84</v>
       </c>
       <c r="F219" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A220" s="3" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A220" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="B220" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C220" s="3">
         <v>22</v>
@@ -6782,15 +6783,15 @@
         <v>43</v>
       </c>
       <c r="F220" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A221" s="3" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A221" s="3" t="s">
-        <v>463</v>
-      </c>
       <c r="B221" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C221" s="3">
         <v>41</v>
@@ -6802,15 +6803,15 @@
         <v>60</v>
       </c>
       <c r="F221" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A222" s="3" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A222" s="3" t="s">
+      <c r="B222" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="C222" s="3">
         <v>47</v>
@@ -6822,15 +6823,15 @@
         <v>51</v>
       </c>
       <c r="F222" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A223" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A223" s="3" t="s">
-        <v>468</v>
-      </c>
       <c r="B223" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C223" s="3">
         <v>52</v>
@@ -6842,15 +6843,15 @@
         <v>41</v>
       </c>
       <c r="F223" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A224" s="3" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A224" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="B224" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C224" s="3">
         <v>44</v>
@@ -6862,15 +6863,15 @@
         <v>40</v>
       </c>
       <c r="F224" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A225" s="3" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A225" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="B225" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C225" s="3">
         <v>36</v>
@@ -6882,15 +6883,15 @@
         <v>57</v>
       </c>
       <c r="F225" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+      <c r="A226" s="3" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.1">
-      <c r="A226" s="3" t="s">
+      <c r="B226" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="C226" s="3">
         <v>77</v>
@@ -6902,15 +6903,15 @@
         <v>63</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A227" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C227" s="3">
         <v>79</v>
@@ -6922,15 +6923,15 @@
         <v>43</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A228" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C228" s="3">
         <v>89</v>
@@ -6942,15 +6943,15 @@
         <v>77</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.1">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A229" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C229" s="3">
         <v>85</v>
@@ -6962,15 +6963,15 @@
         <v>41</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A230" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C230" s="3">
         <v>84</v>
@@ -6982,15 +6983,15 @@
         <v>72</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
       <c r="A231" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C231" s="3">
         <v>73</v>
@@ -7002,11 +7003,17 @@
         <v>81</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="DeNA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7208,20 +7215,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7238,14 +7245,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7254,4 +7253,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/野手能力データ_最新.xlsx
+++ b/野手能力データ_最新.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakahisaFuji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A8C4448-402C-2E49-927D-F51428A20750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF34AB94-664C-43E4-B489-79FBE330FA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="490">
   <si>
     <t>選手名</t>
   </si>
@@ -206,9 +206,6 @@
     <t>菊池涼介</t>
   </si>
   <si>
-    <t>2B:55</t>
-  </si>
-  <si>
     <t>藤原恭大</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
     <t>C:82</t>
   </si>
   <si>
+    <t>宮崎敏郎</t>
+  </si>
+  <si>
     <t>3B:48</t>
   </si>
   <si>
@@ -431,9 +431,6 @@
     <t>森友哉</t>
   </si>
   <si>
-    <t>C:38</t>
-  </si>
-  <si>
     <t>奈良間大己</t>
   </si>
   <si>
@@ -968,9 +965,6 @@
     <t>LF:66 / CF:51 / RF:75</t>
   </si>
   <si>
-    <t>2B:60 / 3B:55 / SS:55</t>
-  </si>
-  <si>
     <t>2B:35 / 3B:35 / SS:41</t>
   </si>
   <si>
@@ -1031,15 +1025,9 @@
     <t>2B:34 / 3B:54 / SS:48</t>
   </si>
   <si>
-    <t>1B:32 / LF:32</t>
-  </si>
-  <si>
     <t>2B:50 / SS:55</t>
   </si>
   <si>
-    <t>C:41 / 1B:49 / 3B:38</t>
-  </si>
-  <si>
     <t>3B:59 / CF:21</t>
   </si>
   <si>
@@ -1130,10 +1118,6 @@
   </si>
   <si>
     <t>LF:51</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1B:35</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1988,7 +1972,28 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>宮﨑敏郎</t>
+    <t>1B:27 / LF:27</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:41 / 1B:49 / 3B:40</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2B:58</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:43</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2B:60 / 3B:55 / SS:60</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1B:47</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -2086,6 +2091,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2375,18 +2384,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F231"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.99609375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="53.04296875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="15" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="53" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2406,7 +2415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2414,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2">
         <v>84</v>
@@ -2423,10 +2432,10 @@
         <v>66</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -2434,19 +2443,19 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2">
         <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2463,10 +2472,10 @@
         <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2483,10 +2492,10 @@
         <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2503,10 +2512,10 @@
         <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2523,10 +2532,10 @@
         <v>56</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2546,7 +2555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2554,19 +2563,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2">
         <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -2583,10 +2592,10 @@
         <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -2603,10 +2612,10 @@
         <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2623,10 +2632,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -2643,10 +2652,10 @@
         <v>34</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2663,10 +2672,10 @@
         <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -2683,10 +2692,10 @@
         <v>78</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -2703,10 +2712,10 @@
         <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
@@ -2723,10 +2732,10 @@
         <v>61</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -2743,12 +2752,12 @@
         <v>32</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>39</v>
@@ -2763,10 +2772,10 @@
         <v>72</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2783,10 +2792,10 @@
         <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -2803,10 +2812,10 @@
         <v>32</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -2823,12 +2832,12 @@
         <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2843,10 +2852,10 @@
         <v>73</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -2863,10 +2872,10 @@
         <v>55</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -2883,10 +2892,10 @@
         <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -2903,10 +2912,10 @@
         <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -2923,10 +2932,10 @@
         <v>70</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -2943,10 +2952,10 @@
         <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -2954,7 +2963,7 @@
         <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D29" s="2">
         <v>78</v>
@@ -2963,12 +2972,12 @@
         <v>37</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>39</v>
@@ -2977,18 +2986,18 @@
         <v>65</v>
       </c>
       <c r="D30" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" s="2">
         <v>28</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>7</v>
@@ -3003,10 +3012,10 @@
         <v>77</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -3026,7 +3035,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -3043,10 +3052,10 @@
         <v>62</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -3063,10 +3072,10 @@
         <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -3077,18 +3086,18 @@
         <v>52</v>
       </c>
       <c r="D35" s="2">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E35" s="2">
         <v>58</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>27</v>
@@ -3103,12 +3112,12 @@
         <v>79</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3123,12 +3132,12 @@
         <v>39</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A38" s="2" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
-      <c r="A38" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>49</v>
@@ -3143,10 +3152,10 @@
         <v>54</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
@@ -3163,12 +3172,12 @@
         <v>60</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>29</v>
@@ -3183,12 +3192,12 @@
         <v>61</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>41</v>
@@ -3203,12 +3212,12 @@
         <v>21</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>29</v>
@@ -3223,10 +3232,10 @@
         <v>32</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
@@ -3234,10 +3243,10 @@
         <v>39</v>
       </c>
       <c r="C43" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D43" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2">
         <v>73</v>
@@ -3246,7 +3255,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -3263,12 +3272,12 @@
         <v>55</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>9</v>
@@ -3277,16 +3286,16 @@
         <v>51</v>
       </c>
       <c r="D45" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E45" s="2">
         <v>52</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -3303,10 +3312,10 @@
         <v>40</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -3314,21 +3323,21 @@
         <v>43</v>
       </c>
       <c r="C47" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D47" s="2">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E47" s="2">
         <v>50</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>9</v>
@@ -3337,18 +3346,18 @@
         <v>49</v>
       </c>
       <c r="D48" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E48" s="2">
         <v>42</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>11</v>
@@ -3363,12 +3372,12 @@
         <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>27</v>
@@ -3383,12 +3392,12 @@
         <v>33</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>43</v>
@@ -3400,15 +3409,15 @@
         <v>50</v>
       </c>
       <c r="E51" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>33</v>
@@ -3423,10 +3432,10 @@
         <v>70</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
         <v>95</v>
       </c>
@@ -3443,12 +3452,12 @@
         <v>24</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>41</v>
@@ -3463,12 +3472,12 @@
         <v>80</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>9</v>
@@ -3477,18 +3486,18 @@
         <v>60</v>
       </c>
       <c r="D55" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E55" s="2">
         <v>48</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>43</v>
@@ -3503,12 +3512,12 @@
         <v>45</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3523,32 +3532,32 @@
         <v>51</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C58" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D58" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E58" s="2">
         <v>46</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>27</v>
@@ -3563,12 +3572,12 @@
         <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>11</v>
@@ -3583,10 +3592,10 @@
         <v>71</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
         <v>96</v>
       </c>
@@ -3603,10 +3612,10 @@
         <v>34</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
         <v>97</v>
       </c>
@@ -3614,7 +3623,7 @@
         <v>9</v>
       </c>
       <c r="C62" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2">
         <v>58</v>
@@ -3623,10 +3632,10 @@
         <v>47</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
         <v>126</v>
       </c>
@@ -3643,12 +3652,12 @@
         <v>30</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>27</v>
@@ -3663,12 +3672,12 @@
         <v>66</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>39</v>
@@ -3683,12 +3692,12 @@
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>41</v>
@@ -3703,12 +3712,12 @@
         <v>90</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>49</v>
@@ -3723,12 +3732,12 @@
         <v>30</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>41</v>
@@ -3743,12 +3752,12 @@
         <v>34</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>489</v>
+        <v>93</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>29</v>
@@ -3766,9 +3775,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>49</v>
@@ -3783,10 +3792,10 @@
         <v>30</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
         <v>98</v>
       </c>
@@ -3806,7 +3815,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
         <v>113</v>
       </c>
@@ -3823,10 +3832,10 @@
         <v>66</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
         <v>125</v>
       </c>
@@ -3843,10 +3852,10 @@
         <v>52</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
         <v>102</v>
       </c>
@@ -3863,10 +3872,10 @@
         <v>53</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
         <v>107</v>
       </c>
@@ -3883,10 +3892,10 @@
         <v>30</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
         <v>105</v>
       </c>
@@ -3906,7 +3915,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
         <v>121</v>
       </c>
@@ -3923,12 +3932,12 @@
         <v>58</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -3943,12 +3952,12 @@
         <v>42</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>33</v>
@@ -3963,10 +3972,10 @@
         <v>41</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
         <v>108</v>
       </c>
@@ -3986,7 +3995,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
         <v>110</v>
       </c>
@@ -4003,10 +4012,10 @@
         <v>26</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
         <v>112</v>
       </c>
@@ -4023,12 +4032,12 @@
         <v>49</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>49</v>
@@ -4043,10 +4052,10 @@
         <v>40</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
         <v>130</v>
       </c>
@@ -4063,12 +4072,12 @@
         <v>46</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>43</v>
@@ -4083,10 +4092,10 @@
         <v>52</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
         <v>104</v>
       </c>
@@ -4097,16 +4106,16 @@
         <v>46</v>
       </c>
       <c r="D86" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E86" s="2">
         <v>78</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
         <v>114</v>
       </c>
@@ -4123,10 +4132,10 @@
         <v>71</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
         <v>115</v>
       </c>
@@ -4143,10 +4152,10 @@
         <v>77</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
         <v>128</v>
       </c>
@@ -4163,12 +4172,12 @@
         <v>85</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>9</v>
@@ -4183,12 +4192,12 @@
         <v>58</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>29</v>
@@ -4203,12 +4212,12 @@
         <v>54</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>14</v>
@@ -4223,10 +4232,10 @@
         <v>48</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
         <v>101</v>
       </c>
@@ -4243,10 +4252,10 @@
         <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
         <v>117</v>
       </c>
@@ -4263,10 +4272,10 @@
         <v>30</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
         <v>122</v>
       </c>
@@ -4283,12 +4292,12 @@
         <v>34</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>49</v>
@@ -4303,12 +4312,12 @@
         <v>71</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>9</v>
@@ -4323,12 +4332,12 @@
         <v>29</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>9</v>
@@ -4343,10 +4352,10 @@
         <v>41</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
         <v>103</v>
       </c>
@@ -4363,10 +4372,10 @@
         <v>36</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
         <v>116</v>
       </c>
@@ -4374,7 +4383,7 @@
         <v>49</v>
       </c>
       <c r="C100" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D100" s="2">
         <v>76</v>
@@ -4383,12 +4392,12 @@
         <v>27</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>11</v>
@@ -4403,12 +4412,12 @@
         <v>77</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>7</v>
@@ -4423,12 +4432,12 @@
         <v>53</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>41</v>
@@ -4443,12 +4452,12 @@
         <v>66</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>49</v>
@@ -4463,10 +4472,10 @@
         <v>41</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
         <v>100</v>
       </c>
@@ -4483,10 +4492,10 @@
         <v>73</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
         <v>120</v>
       </c>
@@ -4503,10 +4512,10 @@
         <v>77</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
         <v>124</v>
       </c>
@@ -4523,10 +4532,10 @@
         <v>58</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
         <v>127</v>
       </c>
@@ -4543,12 +4552,12 @@
         <v>71</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>39</v>
@@ -4563,12 +4572,12 @@
         <v>30</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>39</v>
@@ -4583,12 +4592,12 @@
         <v>71</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>7</v>
@@ -4603,12 +4612,12 @@
         <v>31</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -4623,12 +4632,12 @@
         <v>30</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>33</v>
@@ -4643,10 +4652,10 @@
         <v>30</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
         <v>111</v>
       </c>
@@ -4663,10 +4672,10 @@
         <v>66</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
         <v>118</v>
       </c>
@@ -4686,7 +4695,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
         <v>129</v>
       </c>
@@ -4703,12 +4712,12 @@
         <v>28</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
@@ -4723,12 +4732,12 @@
         <v>71</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>33</v>
@@ -4743,12 +4752,12 @@
         <v>30</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>49</v>
@@ -4763,12 +4772,12 @@
         <v>60</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>9</v>
@@ -4783,12 +4792,12 @@
         <v>56</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>39</v>
@@ -4803,12 +4812,12 @@
         <v>75</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>7</v>
@@ -4823,12 +4832,12 @@
         <v>82</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>9</v>
@@ -4843,12 +4852,12 @@
         <v>78</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>33</v>
@@ -4863,10 +4872,10 @@
         <v>41</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
         <v>123</v>
       </c>
@@ -4883,12 +4892,12 @@
         <v>58</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>39</v>
@@ -4903,12 +4912,12 @@
         <v>58</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>43</v>
@@ -4923,12 +4932,12 @@
         <v>30</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>49</v>
@@ -4943,12 +4952,12 @@
         <v>34</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>33</v>
@@ -4963,12 +4972,12 @@
         <v>66</v>
       </c>
       <c r="F129" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="2" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
-      <c r="A130" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>16</v>
@@ -4983,12 +4992,12 @@
         <v>70</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>14</v>
@@ -5003,12 +5012,12 @@
         <v>67</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>33</v>
@@ -5023,12 +5032,12 @@
         <v>55</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>9</v>
@@ -5043,12 +5052,12 @@
         <v>70</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>33</v>
@@ -5063,12 +5072,12 @@
         <v>37</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>29</v>
@@ -5083,12 +5092,12 @@
         <v>72</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>29</v>
@@ -5103,18 +5112,18 @@
         <v>80</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C137" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D137" s="2">
         <v>38</v>
@@ -5123,12 +5132,12 @@
         <v>72</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>7</v>
@@ -5143,12 +5152,12 @@
         <v>35</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>27</v>
@@ -5163,12 +5172,12 @@
         <v>30</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>16</v>
@@ -5183,12 +5192,12 @@
         <v>48</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>27</v>
@@ -5203,12 +5212,12 @@
         <v>72</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>29</v>
@@ -5223,12 +5232,12 @@
         <v>28</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>14</v>
@@ -5243,12 +5252,12 @@
         <v>69</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>7</v>
@@ -5263,12 +5272,12 @@
         <v>46</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>9</v>
@@ -5283,12 +5292,12 @@
         <v>30</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>49</v>
@@ -5303,12 +5312,12 @@
         <v>49</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>9</v>
@@ -5323,12 +5332,12 @@
         <v>94</v>
       </c>
       <c r="F147" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="2" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
-      <c r="A148" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>43</v>
@@ -5343,12 +5352,12 @@
         <v>61</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>14</v>
@@ -5363,12 +5372,12 @@
         <v>30</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>7</v>
@@ -5383,12 +5392,12 @@
         <v>76</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>14</v>
@@ -5403,12 +5412,12 @@
         <v>21</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>11</v>
@@ -5423,12 +5432,12 @@
         <v>69</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>29</v>
@@ -5443,12 +5452,12 @@
         <v>71</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>7</v>
@@ -5463,12 +5472,12 @@
         <v>26</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>27</v>
@@ -5483,38 +5492,38 @@
         <v>44</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C156" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D156" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E156" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C157" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D157" s="2">
         <v>39</v>
@@ -5523,12 +5532,12 @@
         <v>61</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>14</v>
@@ -5543,12 +5552,12 @@
         <v>56</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>16</v>
@@ -5563,12 +5572,12 @@
         <v>80</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>7</v>
@@ -5583,12 +5592,12 @@
         <v>70</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>27</v>
@@ -5603,12 +5612,12 @@
         <v>74</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>9</v>
@@ -5623,12 +5632,12 @@
         <v>78</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>11</v>
@@ -5643,12 +5652,12 @@
         <v>59</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>33</v>
@@ -5663,12 +5672,12 @@
         <v>71</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>16</v>
@@ -5683,12 +5692,12 @@
         <v>30</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>33</v>
@@ -5703,12 +5712,12 @@
         <v>52</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>43</v>
@@ -5723,12 +5732,12 @@
         <v>61</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>43</v>
@@ -5743,12 +5752,12 @@
         <v>32</v>
       </c>
       <c r="F168" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="2" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
-      <c r="A169" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>16</v>
@@ -5763,12 +5772,12 @@
         <v>30</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>9</v>
@@ -5783,12 +5792,12 @@
         <v>71</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>7</v>
@@ -5803,12 +5812,12 @@
         <v>52</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>41</v>
@@ -5823,12 +5832,12 @@
         <v>40</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>41</v>
@@ -5843,12 +5852,12 @@
         <v>55</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>43</v>
@@ -5857,18 +5866,18 @@
         <v>36</v>
       </c>
       <c r="D174" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E174" s="2">
         <v>66</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>16</v>
@@ -5883,12 +5892,12 @@
         <v>30</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>16</v>
@@ -5903,12 +5912,12 @@
         <v>45</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>11</v>
@@ -5923,12 +5932,12 @@
         <v>30</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>43</v>
@@ -5943,35 +5952,35 @@
         <v>95</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A179" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C179" s="3">
         <v>42</v>
       </c>
       <c r="D179" s="3">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E179" s="3">
         <v>69</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A180" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C180" s="3">
         <v>39</v>
@@ -5983,15 +5992,15 @@
         <v>82</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A181" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C181" s="3">
         <v>18</v>
@@ -6003,15 +6012,15 @@
         <v>28</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A182" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C182" s="3">
         <v>33</v>
@@ -6023,15 +6032,15 @@
         <v>37</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A183" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C183" s="3">
         <v>31</v>
@@ -6043,15 +6052,15 @@
         <v>51</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A184" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C184" s="3">
         <v>38</v>
@@ -6063,15 +6072,15 @@
         <v>69</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A185" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C185" s="3">
         <v>31</v>
@@ -6083,15 +6092,15 @@
         <v>46</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.1">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A186" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C186" s="3">
         <v>44</v>
@@ -6103,15 +6112,15 @@
         <v>25</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.1">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C187" s="3">
         <v>39</v>
@@ -6123,15 +6132,15 @@
         <v>68</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.1">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A188" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C188" s="3">
         <v>57</v>
@@ -6143,15 +6152,15 @@
         <v>58</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A189" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C189" s="3">
         <v>42</v>
@@ -6163,15 +6172,15 @@
         <v>70</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A190" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C190" s="3">
         <v>16</v>
@@ -6183,15 +6192,15 @@
         <v>54</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A191" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C191" s="3">
         <v>28</v>
@@ -6203,15 +6212,15 @@
         <v>66</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C192" s="3">
         <v>52</v>
@@ -6223,15 +6232,15 @@
         <v>38</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A193" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C193" s="3">
         <v>44</v>
@@ -6243,15 +6252,15 @@
         <v>61</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A194" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C194" s="3">
         <v>39</v>
@@ -6263,15 +6272,15 @@
         <v>68</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A195" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C195" s="3">
         <v>42</v>
@@ -6283,15 +6292,15 @@
         <v>64</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A196" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C196" s="3">
         <v>50</v>
@@ -6303,15 +6312,15 @@
         <v>41</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A197" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C197" s="3">
         <v>15</v>
@@ -6323,15 +6332,15 @@
         <v>28</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A198" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C198" s="3">
         <v>41</v>
@@ -6343,15 +6352,15 @@
         <v>80</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A199" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C199" s="3">
         <v>54</v>
@@ -6363,15 +6372,15 @@
         <v>43</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A200" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C200" s="3">
         <v>57</v>
@@ -6383,15 +6392,15 @@
         <v>60</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A201" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C201" s="3">
         <v>49</v>
@@ -6403,15 +6412,15 @@
         <v>51</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A202" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C202" s="3">
         <v>43</v>
@@ -6423,15 +6432,15 @@
         <v>59</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A203" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C203" s="3">
         <v>42</v>
@@ -6443,15 +6452,15 @@
         <v>63</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A204" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C204" s="3">
         <v>46</v>
@@ -6463,15 +6472,15 @@
         <v>55</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A205" s="3" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C205" s="3">
         <v>36</v>
@@ -6483,15 +6492,15 @@
         <v>41</v>
       </c>
       <c r="F205" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A206" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B206" s="3" t="s">
         <v>424</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
-      <c r="A206" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="C206" s="3">
         <v>37</v>
@@ -6503,15 +6512,15 @@
         <v>66</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A207" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C207" s="3">
         <v>35</v>
@@ -6523,15 +6532,15 @@
         <v>51</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A208" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C208" s="3">
         <v>41</v>
@@ -6543,15 +6552,15 @@
         <v>48</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A209" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C209" s="3">
         <v>45</v>
@@ -6563,15 +6572,15 @@
         <v>79</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A210" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C210" s="3">
         <v>59</v>
@@ -6583,15 +6592,15 @@
         <v>44</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A211" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C211" s="3">
         <v>46</v>
@@ -6603,15 +6612,15 @@
         <v>22</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A212" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C212" s="3">
         <v>57</v>
@@ -6623,15 +6632,15 @@
         <v>41</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A213" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C213" s="3">
         <v>36</v>
@@ -6643,15 +6652,15 @@
         <v>55</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A214" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C214" s="3">
         <v>38</v>
@@ -6663,15 +6672,15 @@
         <v>57</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A215" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C215" s="3">
         <v>42</v>
@@ -6683,15 +6692,15 @@
         <v>66</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A216" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C216" s="3">
         <v>41</v>
@@ -6703,15 +6712,15 @@
         <v>91</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A217" s="3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C217" s="3">
         <v>28</v>
@@ -6723,15 +6732,15 @@
         <v>80</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A218" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C218" s="3">
         <v>51</v>
@@ -6743,15 +6752,15 @@
         <v>48</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A219" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C219" s="3">
         <v>29</v>
@@ -6763,15 +6772,15 @@
         <v>84</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A220" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C220" s="3">
         <v>22</v>
@@ -6783,15 +6792,15 @@
         <v>43</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A221" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C221" s="3">
         <v>41</v>
@@ -6803,15 +6812,15 @@
         <v>60</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A222" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C222" s="3">
         <v>47</v>
@@ -6823,15 +6832,15 @@
         <v>51</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A223" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C223" s="3">
         <v>52</v>
@@ -6843,15 +6852,15 @@
         <v>41</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A224" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C224" s="3">
         <v>44</v>
@@ -6863,15 +6872,15 @@
         <v>40</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A225" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C225" s="3">
         <v>36</v>
@@ -6883,15 +6892,15 @@
         <v>57</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A226" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C226" s="3">
         <v>77</v>
@@ -6903,15 +6912,15 @@
         <v>63</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A227" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C227" s="3">
         <v>79</v>
@@ -6923,15 +6932,15 @@
         <v>43</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A228" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C228" s="3">
         <v>89</v>
@@ -6943,15 +6952,15 @@
         <v>77</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A229" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C229" s="3">
         <v>85</v>
@@ -6963,15 +6972,15 @@
         <v>41</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A230" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C230" s="3">
         <v>84</v>
@@ -6983,15 +6992,15 @@
         <v>72</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.1">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A231" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C231" s="3">
         <v>73</v>
@@ -7003,14 +7012,14 @@
         <v>81</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:B231" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="DeNA"/>
+        <filter val="中日"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7020,6 +7029,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B56F6E2A19A2F74190C4E1D46B40D305" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="41a44f59d3b68d1f18012b98926b6f28">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xmlns:ns4="1212b74f-52fc-4973-8f22-7750ea9e0eb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e80f7c3813526ed05737851d7f7b407" ns3:_="" ns4:_="">
     <xsd:import namespace="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
@@ -7214,24 +7240,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6C3AB4F-6546-4A10-9B21-424D4E5F957B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7240,25 +7274,13 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
     <ds:schemaRef ds:uri="1212b74f-52fc-4973-8f22-7750ea9e0eb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA3F5697-8B05-4A8D-92B9-A7AA76646B37}">
-  <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bbf84bfc-8b2c-46e7-9c39-36ecaa6412bf"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC9C7CA-DD2C-4D8C-A9D3-8A8E750B0E4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>